--- a/document/config/ring_case.xlsx
+++ b/document/config/ring_case.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22995" windowHeight="9855" firstSheet="2"/>
+    <workbookView windowWidth="21390" windowHeight="10920" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="连线网表" sheetId="3" r:id="rId1"/>
@@ -4230,6 +4230,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -5323,7 +5330,7 @@
       <c r="C38" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="17">
         <v>3</v>
       </c>
       <c r="F38" s="1"/>
@@ -5333,8 +5340,8 @@
       <c r="H38" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="14">
-        <v>3</v>
+      <c r="I38" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="2:9">
@@ -5355,7 +5362,7 @@
         <v>81</v>
       </c>
       <c r="I39" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="2:9">
@@ -5365,7 +5372,7 @@
       <c r="C40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="17">
         <v>3</v>
       </c>
       <c r="F40" s="1"/>
@@ -5375,8 +5382,8 @@
       <c r="H40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I40" s="14">
-        <v>3</v>
+      <c r="I40" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="2:9">
@@ -5397,7 +5404,7 @@
         <v>87</v>
       </c>
       <c r="I41" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="2:9">
@@ -5407,7 +5414,7 @@
       <c r="C42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="17">
         <v>3</v>
       </c>
       <c r="F42" s="1"/>
@@ -5417,8 +5424,8 @@
       <c r="H42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I42" s="14">
-        <v>3</v>
+      <c r="I42" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="2:9">
@@ -5439,7 +5446,7 @@
         <v>93</v>
       </c>
       <c r="I43" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="2:9">
@@ -5449,7 +5456,7 @@
       <c r="C44" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="17">
         <v>3</v>
       </c>
       <c r="F44" s="1"/>
@@ -5459,8 +5466,8 @@
       <c r="H44" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I44" s="14">
-        <v>3</v>
+      <c r="I44" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="2:9">
@@ -5481,7 +5488,7 @@
         <v>99</v>
       </c>
       <c r="I45" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="2:9">
@@ -5491,7 +5498,7 @@
       <c r="C46" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="17">
         <v>3</v>
       </c>
       <c r="F46" s="1"/>
@@ -5501,8 +5508,8 @@
       <c r="H46" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I46" s="14">
-        <v>3</v>
+      <c r="I46" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="2:9">
@@ -5523,7 +5530,7 @@
         <v>105</v>
       </c>
       <c r="I47" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="2:9">
@@ -5533,7 +5540,7 @@
       <c r="C48" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="17">
         <v>3</v>
       </c>
       <c r="F48" s="1"/>
@@ -5543,8 +5550,8 @@
       <c r="H48" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I48" s="14">
-        <v>3</v>
+      <c r="I48" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="2:9">
@@ -5565,7 +5572,7 @@
         <v>111</v>
       </c>
       <c r="I49" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="2:9">
@@ -5575,8 +5582,8 @@
       <c r="C50" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="23">
-        <v>4</v>
+      <c r="D50" s="17">
+        <v>6</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="21" t="s">
@@ -5585,8 +5592,8 @@
       <c r="H50" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="I50" s="23">
-        <v>4</v>
+      <c r="I50" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="2:9">
@@ -5597,7 +5604,7 @@
         <v>117</v>
       </c>
       <c r="D51" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="16" t="s">
@@ -5607,7 +5614,7 @@
         <v>118</v>
       </c>
       <c r="I51" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="2:9">
@@ -5617,8 +5624,8 @@
       <c r="C52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="23">
-        <v>4</v>
+      <c r="D52" s="17">
+        <v>6</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="16" t="s">
@@ -5627,8 +5634,8 @@
       <c r="H52" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I52" s="23">
-        <v>4</v>
+      <c r="I52" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="2:9">
@@ -5639,7 +5646,7 @@
         <v>123</v>
       </c>
       <c r="D53" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="16" t="s">
@@ -5649,7 +5656,7 @@
         <v>124</v>
       </c>
       <c r="I53" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="2:9">
@@ -5659,8 +5666,8 @@
       <c r="C54" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="23">
-        <v>4</v>
+      <c r="D54" s="17">
+        <v>6</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="16" t="s">
@@ -5669,8 +5676,8 @@
       <c r="H54" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I54" s="23">
-        <v>4</v>
+      <c r="I54" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="2:9">
@@ -5681,7 +5688,7 @@
         <v>129</v>
       </c>
       <c r="D55" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="16" t="s">
@@ -5691,7 +5698,7 @@
         <v>130</v>
       </c>
       <c r="I55" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="2:9">
@@ -5701,8 +5708,8 @@
       <c r="C56" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="23">
-        <v>4</v>
+      <c r="D56" s="17">
+        <v>6</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="16" t="s">
@@ -5711,8 +5718,8 @@
       <c r="H56" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I56" s="23">
-        <v>4</v>
+      <c r="I56" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="2:9">
@@ -5723,7 +5730,7 @@
         <v>135</v>
       </c>
       <c r="D57" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="16" t="s">
@@ -5733,7 +5740,7 @@
         <v>136</v>
       </c>
       <c r="I57" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="2:9">
@@ -5743,8 +5750,8 @@
       <c r="C58" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D58" s="23">
-        <v>4</v>
+      <c r="D58" s="17">
+        <v>6</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>137</v>
@@ -5752,8 +5759,8 @@
       <c r="H58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="23">
-        <v>4</v>
+      <c r="I58" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="2:9">
@@ -5764,7 +5771,7 @@
         <v>141</v>
       </c>
       <c r="D59" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>140</v>
@@ -5773,7 +5780,7 @@
         <v>142</v>
       </c>
       <c r="I59" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="2:9">
@@ -5783,8 +5790,8 @@
       <c r="C60" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D60" s="23">
-        <v>4</v>
+      <c r="D60" s="17">
+        <v>6</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>143</v>
@@ -5792,8 +5799,8 @@
       <c r="H60" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I60" s="23">
-        <v>4</v>
+      <c r="I60" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="2:9">
@@ -5804,7 +5811,7 @@
         <v>147</v>
       </c>
       <c r="D61" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>146</v>
@@ -5813,7 +5820,7 @@
         <v>148</v>
       </c>
       <c r="I61" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="2:9">
@@ -5823,8 +5830,8 @@
       <c r="C62" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D62" s="23">
-        <v>4</v>
+      <c r="D62" s="17">
+        <v>6</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>149</v>
@@ -5832,8 +5839,8 @@
       <c r="H62" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I62" s="23">
-        <v>4</v>
+      <c r="I62" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="2:9">
@@ -5844,7 +5851,7 @@
         <v>153</v>
       </c>
       <c r="D63" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>152</v>
@@ -5853,7 +5860,7 @@
         <v>154</v>
       </c>
       <c r="I63" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="2:9">
@@ -5863,8 +5870,8 @@
       <c r="C64" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D64" s="23">
-        <v>4</v>
+      <c r="D64" s="17">
+        <v>6</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>155</v>
@@ -5872,8 +5879,8 @@
       <c r="H64" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I64" s="23">
-        <v>4</v>
+      <c r="I64" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="2:9">
@@ -5884,7 +5891,7 @@
         <v>159</v>
       </c>
       <c r="D65" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>158</v>
@@ -5893,7 +5900,7 @@
         <v>160</v>
       </c>
       <c r="I65" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="2:9">
@@ -5903,8 +5910,8 @@
       <c r="C66" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D66" s="23">
-        <v>4</v>
+      <c r="D66" s="17">
+        <v>6</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>161</v>
@@ -5912,8 +5919,8 @@
       <c r="H66" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I66" s="23">
-        <v>4</v>
+      <c r="I66" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="2:9">
@@ -5924,7 +5931,7 @@
         <v>165</v>
       </c>
       <c r="D67" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>164</v>
@@ -5933,7 +5940,7 @@
         <v>166</v>
       </c>
       <c r="I67" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="2:9">
@@ -5943,8 +5950,8 @@
       <c r="C68" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D68" s="23">
-        <v>4</v>
+      <c r="D68" s="17">
+        <v>6</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>167</v>
@@ -5952,8 +5959,8 @@
       <c r="H68" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I68" s="23">
-        <v>4</v>
+      <c r="I68" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="2:9">
@@ -5964,7 +5971,7 @@
         <v>171</v>
       </c>
       <c r="D69" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G69" s="24" t="s">
         <v>170</v>
@@ -5973,7 +5980,7 @@
         <v>172</v>
       </c>
       <c r="I69" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="2:9">
@@ -5983,8 +5990,8 @@
       <c r="C70" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D70" s="14">
-        <v>6</v>
+      <c r="D70" s="17">
+        <v>8</v>
       </c>
       <c r="G70" s="12" t="s">
         <v>175</v>
@@ -5992,8 +5999,8 @@
       <c r="H70" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="I70" s="14">
-        <v>6</v>
+      <c r="I70" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="2:9">
@@ -6004,7 +6011,7 @@
         <v>178</v>
       </c>
       <c r="D71" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>179</v>
@@ -6013,7 +6020,7 @@
         <v>180</v>
       </c>
       <c r="I71" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="2:9">
@@ -6023,8 +6030,8 @@
       <c r="C72" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D72" s="14">
-        <v>6</v>
+      <c r="D72" s="17">
+        <v>8</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>183</v>
@@ -6032,8 +6039,8 @@
       <c r="H72" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I72" s="14">
-        <v>6</v>
+      <c r="I72" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="2:9">
@@ -6044,7 +6051,7 @@
         <v>186</v>
       </c>
       <c r="D73" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>187</v>
@@ -6053,7 +6060,7 @@
         <v>188</v>
       </c>
       <c r="I73" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="2:9">
@@ -6063,8 +6070,8 @@
       <c r="C74" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D74" s="14">
-        <v>6</v>
+      <c r="D74" s="17">
+        <v>8</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>191</v>
@@ -6072,8 +6079,8 @@
       <c r="H74" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="I74" s="14">
-        <v>6</v>
+      <c r="I74" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="2:9">
@@ -6084,7 +6091,7 @@
         <v>194</v>
       </c>
       <c r="D75" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>195</v>
@@ -6093,7 +6100,7 @@
         <v>196</v>
       </c>
       <c r="I75" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="2:9">
@@ -6103,8 +6110,8 @@
       <c r="C76" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="14">
-        <v>6</v>
+      <c r="D76" s="17">
+        <v>8</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>199</v>
@@ -6112,8 +6119,8 @@
       <c r="H76" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="14">
-        <v>6</v>
+      <c r="I76" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="2:9">
@@ -6124,7 +6131,7 @@
         <v>202</v>
       </c>
       <c r="D77" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>203</v>
@@ -6133,7 +6140,7 @@
         <v>204</v>
       </c>
       <c r="I77" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="2:9">
@@ -6143,8 +6150,8 @@
       <c r="C78" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D78" s="14">
-        <v>6</v>
+      <c r="D78" s="17">
+        <v>8</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>207</v>
@@ -6152,8 +6159,8 @@
       <c r="H78" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="I78" s="14">
-        <v>6</v>
+      <c r="I78" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="2:9">
@@ -6164,7 +6171,7 @@
         <v>210</v>
       </c>
       <c r="D79" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>211</v>
@@ -6173,7 +6180,7 @@
         <v>212</v>
       </c>
       <c r="I79" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="2:9">
@@ -6183,8 +6190,8 @@
       <c r="C80" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D80" s="14">
-        <v>6</v>
+      <c r="D80" s="17">
+        <v>8</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>215</v>
@@ -6192,8 +6199,8 @@
       <c r="H80" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I80" s="14">
-        <v>6</v>
+      <c r="I80" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="2:9">
@@ -6204,7 +6211,7 @@
         <v>218</v>
       </c>
       <c r="D81" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G81" s="18" t="s">
         <v>219</v>
@@ -6213,7 +6220,7 @@
         <v>220</v>
       </c>
       <c r="I81" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="2:9">
@@ -6223,8 +6230,8 @@
       <c r="C82" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="D82" s="23">
-        <v>7</v>
+      <c r="D82" s="17">
+        <v>10</v>
       </c>
       <c r="G82" s="21" t="s">
         <v>223</v>
@@ -6232,8 +6239,8 @@
       <c r="H82" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="I82" s="23">
-        <v>7</v>
+      <c r="I82" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="2:9">
@@ -6244,7 +6251,7 @@
         <v>226</v>
       </c>
       <c r="D83" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>227</v>
@@ -6253,7 +6260,7 @@
         <v>228</v>
       </c>
       <c r="I83" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="2:9">
@@ -6263,8 +6270,8 @@
       <c r="C84" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D84" s="23">
-        <v>7</v>
+      <c r="D84" s="17">
+        <v>10</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>231</v>
@@ -6272,8 +6279,8 @@
       <c r="H84" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="I84" s="23">
-        <v>7</v>
+      <c r="I84" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="2:9">
@@ -6284,7 +6291,7 @@
         <v>234</v>
       </c>
       <c r="D85" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>235</v>
@@ -6293,7 +6300,7 @@
         <v>236</v>
       </c>
       <c r="I85" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="2:9">
@@ -6303,8 +6310,8 @@
       <c r="C86" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D86" s="23">
-        <v>7</v>
+      <c r="D86" s="17">
+        <v>10</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>239</v>
@@ -6312,8 +6319,8 @@
       <c r="H86" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="I86" s="23">
-        <v>7</v>
+      <c r="I86" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="2:9">
@@ -6324,7 +6331,7 @@
         <v>242</v>
       </c>
       <c r="D87" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>243</v>
@@ -6333,7 +6340,7 @@
         <v>244</v>
       </c>
       <c r="I87" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="2:9">
@@ -6343,8 +6350,8 @@
       <c r="C88" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D88" s="23">
-        <v>7</v>
+      <c r="D88" s="17">
+        <v>10</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>247</v>
@@ -6352,8 +6359,8 @@
       <c r="H88" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="I88" s="23">
-        <v>7</v>
+      <c r="I88" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="2:9">
@@ -6364,7 +6371,7 @@
         <v>250</v>
       </c>
       <c r="D89" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>251</v>
@@ -6373,7 +6380,7 @@
         <v>252</v>
       </c>
       <c r="I89" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="2:9">
@@ -6383,8 +6390,8 @@
       <c r="C90" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D90" s="23">
-        <v>7</v>
+      <c r="D90" s="17">
+        <v>10</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>255</v>
@@ -6392,8 +6399,8 @@
       <c r="H90" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I90" s="23">
-        <v>7</v>
+      <c r="I90" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="2:9">
@@ -6404,7 +6411,7 @@
         <v>258</v>
       </c>
       <c r="D91" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>259</v>
@@ -6413,7 +6420,7 @@
         <v>260</v>
       </c>
       <c r="I91" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="2:9">
@@ -6423,8 +6430,8 @@
       <c r="C92" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D92" s="23">
-        <v>7</v>
+      <c r="D92" s="17">
+        <v>10</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>263</v>
@@ -6432,8 +6439,8 @@
       <c r="H92" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="I92" s="23">
-        <v>7</v>
+      <c r="I92" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="2:9">
@@ -6444,7 +6451,7 @@
         <v>266</v>
       </c>
       <c r="D93" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>267</v>
@@ -6453,7 +6460,7 @@
         <v>268</v>
       </c>
       <c r="I93" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="2:9">
@@ -6463,8 +6470,8 @@
       <c r="C94" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D94" s="23">
-        <v>7</v>
+      <c r="D94" s="17">
+        <v>10</v>
       </c>
       <c r="G94" s="16" t="s">
         <v>271</v>
@@ -6472,8 +6479,8 @@
       <c r="H94" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I94" s="23">
-        <v>7</v>
+      <c r="I94" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="2:9">
@@ -6484,7 +6491,7 @@
         <v>274</v>
       </c>
       <c r="D95" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G95" s="16" t="s">
         <v>275</v>
@@ -6493,7 +6500,7 @@
         <v>276</v>
       </c>
       <c r="I95" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="2:9">
@@ -6503,8 +6510,8 @@
       <c r="C96" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D96" s="23">
-        <v>7</v>
+      <c r="D96" s="17">
+        <v>10</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>279</v>
@@ -6512,8 +6519,8 @@
       <c r="H96" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="I96" s="23">
-        <v>7</v>
+      <c r="I96" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="2:9">
@@ -6524,7 +6531,7 @@
         <v>282</v>
       </c>
       <c r="D97" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G97" s="16" t="s">
         <v>283</v>
@@ -6533,7 +6540,7 @@
         <v>284</v>
       </c>
       <c r="I97" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="2:9">
@@ -6543,8 +6550,8 @@
       <c r="C98" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D98" s="23">
-        <v>7</v>
+      <c r="D98" s="17">
+        <v>10</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>287</v>
@@ -6552,8 +6559,8 @@
       <c r="H98" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="I98" s="23">
-        <v>7</v>
+      <c r="I98" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="2:9">
@@ -6564,7 +6571,7 @@
         <v>290</v>
       </c>
       <c r="D99" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>291</v>
@@ -6573,7 +6580,7 @@
         <v>292</v>
       </c>
       <c r="I99" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="2:9">
@@ -6583,8 +6590,8 @@
       <c r="C100" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D100" s="23">
-        <v>7</v>
+      <c r="D100" s="17">
+        <v>10</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>295</v>
@@ -6592,8 +6599,8 @@
       <c r="H100" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="I100" s="23">
-        <v>7</v>
+      <c r="I100" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="2:9">
@@ -6604,7 +6611,7 @@
         <v>298</v>
       </c>
       <c r="D101" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G101" s="24" t="s">
         <v>299</v>
@@ -6613,7 +6620,7 @@
         <v>300</v>
       </c>
       <c r="I101" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="2:9">
@@ -6623,8 +6630,8 @@
       <c r="C102" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D102" s="14">
-        <v>8</v>
+      <c r="D102" s="17">
+        <v>12</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>303</v>
@@ -6632,8 +6639,8 @@
       <c r="H102" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="I102" s="14">
-        <v>8</v>
+      <c r="I102" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="2:9">
@@ -6644,7 +6651,7 @@
         <v>306</v>
       </c>
       <c r="D103" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>307</v>
@@ -6653,7 +6660,7 @@
         <v>308</v>
       </c>
       <c r="I103" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="2:9">
@@ -6663,8 +6670,8 @@
       <c r="C104" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D104" s="14">
-        <v>8</v>
+      <c r="D104" s="17">
+        <v>12</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>311</v>
@@ -6672,8 +6679,8 @@
       <c r="H104" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="I104" s="14">
-        <v>8</v>
+      <c r="I104" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="2:9">
@@ -6684,7 +6691,7 @@
         <v>314</v>
       </c>
       <c r="D105" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G105" s="16" t="s">
         <v>315</v>
@@ -6693,7 +6700,7 @@
         <v>316</v>
       </c>
       <c r="I105" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="2:9">
@@ -6703,8 +6710,8 @@
       <c r="C106" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D106" s="14">
-        <v>8</v>
+      <c r="D106" s="17">
+        <v>12</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>319</v>
@@ -6712,8 +6719,8 @@
       <c r="H106" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I106" s="14">
-        <v>8</v>
+      <c r="I106" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="2:9">
@@ -6724,7 +6731,7 @@
         <v>322</v>
       </c>
       <c r="D107" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>323</v>
@@ -6733,7 +6740,7 @@
         <v>324</v>
       </c>
       <c r="I107" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="2:9">
@@ -6743,8 +6750,8 @@
       <c r="C108" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D108" s="14">
-        <v>8</v>
+      <c r="D108" s="17">
+        <v>12</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>327</v>
@@ -6752,8 +6759,8 @@
       <c r="H108" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="I108" s="14">
-        <v>8</v>
+      <c r="I108" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="2:9">
@@ -6764,7 +6771,7 @@
         <v>330</v>
       </c>
       <c r="D109" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G109" s="16" t="s">
         <v>331</v>
@@ -6773,7 +6780,7 @@
         <v>332</v>
       </c>
       <c r="I109" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="2:9">
@@ -6783,8 +6790,8 @@
       <c r="C110" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D110" s="14">
-        <v>8</v>
+      <c r="D110" s="17">
+        <v>12</v>
       </c>
       <c r="G110" s="16" t="s">
         <v>335</v>
@@ -6792,8 +6799,8 @@
       <c r="H110" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I110" s="14">
-        <v>8</v>
+      <c r="I110" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="2:9">
@@ -6804,7 +6811,7 @@
         <v>338</v>
       </c>
       <c r="D111" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G111" s="16" t="s">
         <v>339</v>
@@ -6813,7 +6820,7 @@
         <v>340</v>
       </c>
       <c r="I111" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="2:9">
@@ -6823,8 +6830,8 @@
       <c r="C112" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D112" s="14">
-        <v>8</v>
+      <c r="D112" s="17">
+        <v>12</v>
       </c>
       <c r="G112" s="16" t="s">
         <v>343</v>
@@ -6832,8 +6839,8 @@
       <c r="H112" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="I112" s="14">
-        <v>8</v>
+      <c r="I112" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="2:9">
@@ -6844,7 +6851,7 @@
         <v>346</v>
       </c>
       <c r="D113" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G113" s="18" t="s">
         <v>347</v>
@@ -6853,7 +6860,7 @@
         <v>348</v>
       </c>
       <c r="I113" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="2:9">
@@ -6863,8 +6870,8 @@
       <c r="C114" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="D114" s="23">
-        <v>9</v>
+      <c r="D114" s="17">
+        <v>14</v>
       </c>
       <c r="G114" s="21" t="s">
         <v>351</v>
@@ -6872,8 +6879,8 @@
       <c r="H114" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="I114" s="23">
-        <v>9</v>
+      <c r="I114" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="2:9">
@@ -6884,7 +6891,7 @@
         <v>354</v>
       </c>
       <c r="D115" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G115" s="16" t="s">
         <v>355</v>
@@ -6893,7 +6900,7 @@
         <v>356</v>
       </c>
       <c r="I115" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="2:9">
@@ -6903,8 +6910,8 @@
       <c r="C116" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D116" s="23">
-        <v>9</v>
+      <c r="D116" s="17">
+        <v>14</v>
       </c>
       <c r="G116" s="16" t="s">
         <v>359</v>
@@ -6912,8 +6919,8 @@
       <c r="H116" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="I116" s="23">
-        <v>9</v>
+      <c r="I116" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="2:9">
@@ -6924,7 +6931,7 @@
         <v>362</v>
       </c>
       <c r="D117" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G117" s="16" t="s">
         <v>363</v>
@@ -6933,7 +6940,7 @@
         <v>364</v>
       </c>
       <c r="I117" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="2:9">
@@ -6943,8 +6950,8 @@
       <c r="C118" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D118" s="23">
-        <v>9</v>
+      <c r="D118" s="17">
+        <v>14</v>
       </c>
       <c r="G118" s="16" t="s">
         <v>367</v>
@@ -6952,8 +6959,8 @@
       <c r="H118" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="I118" s="23">
-        <v>9</v>
+      <c r="I118" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="2:9">
@@ -6964,7 +6971,7 @@
         <v>370</v>
       </c>
       <c r="D119" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G119" s="16" t="s">
         <v>371</v>
@@ -6973,7 +6980,7 @@
         <v>372</v>
       </c>
       <c r="I119" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="2:9">
@@ -6983,8 +6990,8 @@
       <c r="C120" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D120" s="23">
-        <v>9</v>
+      <c r="D120" s="17">
+        <v>14</v>
       </c>
       <c r="G120" s="16" t="s">
         <v>375</v>
@@ -6992,8 +6999,8 @@
       <c r="H120" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="I120" s="23">
-        <v>9</v>
+      <c r="I120" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="2:9">
@@ -7004,7 +7011,7 @@
         <v>378</v>
       </c>
       <c r="D121" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G121" s="16" t="s">
         <v>379</v>
@@ -7013,7 +7020,7 @@
         <v>380</v>
       </c>
       <c r="I121" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="2:9">
@@ -7023,8 +7030,8 @@
       <c r="C122" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D122" s="23">
-        <v>9</v>
+      <c r="D122" s="17">
+        <v>14</v>
       </c>
       <c r="G122" s="16" t="s">
         <v>383</v>
@@ -7032,8 +7039,8 @@
       <c r="H122" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="I122" s="23">
-        <v>9</v>
+      <c r="I122" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="2:9">
@@ -7044,7 +7051,7 @@
         <v>386</v>
       </c>
       <c r="D123" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G123" s="16" t="s">
         <v>387</v>
@@ -7053,7 +7060,7 @@
         <v>388</v>
       </c>
       <c r="I123" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="2:9">
@@ -7063,8 +7070,8 @@
       <c r="C124" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D124" s="23">
-        <v>9</v>
+      <c r="D124" s="17">
+        <v>14</v>
       </c>
       <c r="G124" s="16" t="s">
         <v>391</v>
@@ -7072,8 +7079,8 @@
       <c r="H124" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="I124" s="23">
-        <v>9</v>
+      <c r="I124" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="2:9">
@@ -7084,7 +7091,7 @@
         <v>394</v>
       </c>
       <c r="D125" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G125" s="16" t="s">
         <v>395</v>
@@ -7093,7 +7100,7 @@
         <v>396</v>
       </c>
       <c r="I125" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="2:9">
@@ -7103,8 +7110,8 @@
       <c r="C126" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D126" s="23">
-        <v>9</v>
+      <c r="D126" s="17">
+        <v>14</v>
       </c>
       <c r="G126" s="16" t="s">
         <v>399</v>
@@ -7112,8 +7119,8 @@
       <c r="H126" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I126" s="23">
-        <v>9</v>
+      <c r="I126" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="2:9">
@@ -7124,7 +7131,7 @@
         <v>402</v>
       </c>
       <c r="D127" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G127" s="16" t="s">
         <v>403</v>
@@ -7133,7 +7140,7 @@
         <v>404</v>
       </c>
       <c r="I127" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="2:9">
@@ -7143,8 +7150,8 @@
       <c r="C128" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D128" s="23">
-        <v>9</v>
+      <c r="D128" s="17">
+        <v>14</v>
       </c>
       <c r="G128" s="16" t="s">
         <v>407</v>
@@ -7152,8 +7159,8 @@
       <c r="H128" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="I128" s="23">
-        <v>9</v>
+      <c r="I128" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="2:9">
@@ -7164,7 +7171,7 @@
         <v>410</v>
       </c>
       <c r="D129" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G129" s="16" t="s">
         <v>411</v>
@@ -7173,7 +7180,7 @@
         <v>412</v>
       </c>
       <c r="I129" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="2:9">
@@ -7183,8 +7190,8 @@
       <c r="C130" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D130" s="23">
-        <v>9</v>
+      <c r="D130" s="17">
+        <v>14</v>
       </c>
       <c r="G130" s="16" t="s">
         <v>415</v>
@@ -7192,8 +7199,8 @@
       <c r="H130" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="I130" s="23">
-        <v>9</v>
+      <c r="I130" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="2:9">
@@ -7204,7 +7211,7 @@
         <v>418</v>
       </c>
       <c r="D131" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G131" s="16" t="s">
         <v>419</v>
@@ -7213,7 +7220,7 @@
         <v>420</v>
       </c>
       <c r="I131" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="2:9">
@@ -7223,8 +7230,8 @@
       <c r="C132" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D132" s="23">
-        <v>9</v>
+      <c r="D132" s="17">
+        <v>14</v>
       </c>
       <c r="G132" s="16" t="s">
         <v>423</v>
@@ -7232,8 +7239,8 @@
       <c r="H132" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="I132" s="23">
-        <v>9</v>
+      <c r="I132" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="2:9">
@@ -7244,7 +7251,7 @@
         <v>426</v>
       </c>
       <c r="D133" s="17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G133" s="24" t="s">
         <v>427</v>
@@ -7253,7 +7260,7 @@
         <v>428</v>
       </c>
       <c r="I133" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="2:9">
@@ -7263,8 +7270,8 @@
       <c r="C134" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="D134" s="14">
-        <v>10</v>
+      <c r="D134" s="17">
+        <v>16</v>
       </c>
       <c r="G134" s="15" t="s">
         <v>173</v>
@@ -7272,8 +7279,8 @@
       <c r="H134" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="I134" s="14">
-        <v>10</v>
+      <c r="I134" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="2:9">
@@ -7284,7 +7291,7 @@
         <v>432</v>
       </c>
       <c r="D135" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G135" s="16" t="s">
         <v>177</v>
@@ -7293,7 +7300,7 @@
         <v>178</v>
       </c>
       <c r="I135" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="2:9">
@@ -7303,8 +7310,8 @@
       <c r="C136" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D136" s="14">
-        <v>10</v>
+      <c r="D136" s="17">
+        <v>16</v>
       </c>
       <c r="G136" s="16" t="s">
         <v>181</v>
@@ -7312,8 +7319,8 @@
       <c r="H136" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I136" s="14">
-        <v>10</v>
+      <c r="I136" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="2:9">
@@ -7324,7 +7331,7 @@
         <v>436</v>
       </c>
       <c r="D137" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G137" s="16" t="s">
         <v>185</v>
@@ -7333,7 +7340,7 @@
         <v>186</v>
       </c>
       <c r="I137" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="2:9">
@@ -7343,8 +7350,8 @@
       <c r="C138" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D138" s="14">
-        <v>10</v>
+      <c r="D138" s="17">
+        <v>16</v>
       </c>
       <c r="G138" s="16" t="s">
         <v>189</v>
@@ -7352,8 +7359,8 @@
       <c r="H138" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I138" s="14">
-        <v>10</v>
+      <c r="I138" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="2:9">
@@ -7364,7 +7371,7 @@
         <v>440</v>
       </c>
       <c r="D139" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G139" s="16" t="s">
         <v>193</v>
@@ -7373,7 +7380,7 @@
         <v>194</v>
       </c>
       <c r="I139" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="2:9">
@@ -7383,8 +7390,8 @@
       <c r="C140" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D140" s="14">
-        <v>10</v>
+      <c r="D140" s="17">
+        <v>16</v>
       </c>
       <c r="G140" s="16" t="s">
         <v>197</v>
@@ -7392,8 +7399,8 @@
       <c r="H140" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I140" s="14">
-        <v>10</v>
+      <c r="I140" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="2:9">
@@ -7404,7 +7411,7 @@
         <v>444</v>
       </c>
       <c r="D141" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G141" s="16" t="s">
         <v>201</v>
@@ -7413,7 +7420,7 @@
         <v>202</v>
       </c>
       <c r="I141" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="2:9">
@@ -7423,8 +7430,8 @@
       <c r="C142" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D142" s="14">
-        <v>10</v>
+      <c r="D142" s="17">
+        <v>16</v>
       </c>
       <c r="G142" s="16" t="s">
         <v>205</v>
@@ -7432,8 +7439,8 @@
       <c r="H142" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I142" s="14">
-        <v>10</v>
+      <c r="I142" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="2:9">
@@ -7444,7 +7451,7 @@
         <v>448</v>
       </c>
       <c r="D143" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G143" s="16" t="s">
         <v>209</v>
@@ -7453,7 +7460,7 @@
         <v>210</v>
       </c>
       <c r="I143" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="2:9">
@@ -7463,8 +7470,8 @@
       <c r="C144" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D144" s="14">
-        <v>10</v>
+      <c r="D144" s="17">
+        <v>16</v>
       </c>
       <c r="G144" s="16" t="s">
         <v>213</v>
@@ -7472,8 +7479,8 @@
       <c r="H144" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="I144" s="14">
-        <v>10</v>
+      <c r="I144" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="2:9">
@@ -7484,7 +7491,7 @@
         <v>452</v>
       </c>
       <c r="D145" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G145" s="18" t="s">
         <v>217</v>
@@ -7493,7 +7500,7 @@
         <v>218</v>
       </c>
       <c r="I145" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="2:9">
@@ -7503,8 +7510,8 @@
       <c r="C146" s="22" t="s">
         <v>454</v>
       </c>
-      <c r="D146" s="23">
-        <v>11</v>
+      <c r="D146" s="17">
+        <v>17</v>
       </c>
       <c r="G146" s="21" t="s">
         <v>221</v>
@@ -7512,8 +7519,8 @@
       <c r="H146" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="I146" s="23">
-        <v>11</v>
+      <c r="I146" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="2:9">
@@ -7524,7 +7531,7 @@
         <v>456</v>
       </c>
       <c r="D147" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G147" s="16" t="s">
         <v>225</v>
@@ -7533,7 +7540,7 @@
         <v>226</v>
       </c>
       <c r="I147" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="2:9">
@@ -7543,8 +7550,8 @@
       <c r="C148" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D148" s="23">
-        <v>11</v>
+      <c r="D148" s="17">
+        <v>17</v>
       </c>
       <c r="G148" s="16" t="s">
         <v>229</v>
@@ -7552,8 +7559,8 @@
       <c r="H148" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="I148" s="23">
-        <v>11</v>
+      <c r="I148" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="2:9">
@@ -7564,7 +7571,7 @@
         <v>460</v>
       </c>
       <c r="D149" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G149" s="16" t="s">
         <v>233</v>
@@ -7573,7 +7580,7 @@
         <v>234</v>
       </c>
       <c r="I149" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="2:9">
@@ -7583,8 +7590,8 @@
       <c r="C150" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D150" s="23">
-        <v>11</v>
+      <c r="D150" s="17">
+        <v>17</v>
       </c>
       <c r="G150" s="16" t="s">
         <v>237</v>
@@ -7592,8 +7599,8 @@
       <c r="H150" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I150" s="23">
-        <v>11</v>
+      <c r="I150" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="2:9">
@@ -7604,7 +7611,7 @@
         <v>464</v>
       </c>
       <c r="D151" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G151" s="16" t="s">
         <v>241</v>
@@ -7613,7 +7620,7 @@
         <v>242</v>
       </c>
       <c r="I151" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="2:9">
@@ -7623,8 +7630,8 @@
       <c r="C152" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D152" s="23">
-        <v>11</v>
+      <c r="D152" s="17">
+        <v>17</v>
       </c>
       <c r="G152" s="16" t="s">
         <v>245</v>
@@ -7632,8 +7639,8 @@
       <c r="H152" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I152" s="23">
-        <v>11</v>
+      <c r="I152" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="2:9">
@@ -7644,7 +7651,7 @@
         <v>468</v>
       </c>
       <c r="D153" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G153" s="16" t="s">
         <v>249</v>
@@ -7653,7 +7660,7 @@
         <v>250</v>
       </c>
       <c r="I153" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="2:9">
@@ -7663,8 +7670,8 @@
       <c r="C154" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D154" s="23">
-        <v>11</v>
+      <c r="D154" s="17">
+        <v>17</v>
       </c>
       <c r="G154" s="16" t="s">
         <v>253</v>
@@ -7672,8 +7679,8 @@
       <c r="H154" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="I154" s="23">
-        <v>11</v>
+      <c r="I154" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="2:9">
@@ -7684,7 +7691,7 @@
         <v>472</v>
       </c>
       <c r="D155" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G155" s="16" t="s">
         <v>257</v>
@@ -7693,7 +7700,7 @@
         <v>258</v>
       </c>
       <c r="I155" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="2:9">
@@ -7703,8 +7710,8 @@
       <c r="C156" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D156" s="23">
-        <v>11</v>
+      <c r="D156" s="17">
+        <v>17</v>
       </c>
       <c r="G156" s="16" t="s">
         <v>261</v>
@@ -7712,8 +7719,8 @@
       <c r="H156" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I156" s="23">
-        <v>11</v>
+      <c r="I156" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="2:9">
@@ -7724,7 +7731,7 @@
         <v>476</v>
       </c>
       <c r="D157" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G157" s="16" t="s">
         <v>265</v>
@@ -7733,7 +7740,7 @@
         <v>266</v>
       </c>
       <c r="I157" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="2:9">
@@ -7743,8 +7750,8 @@
       <c r="C158" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D158" s="23">
-        <v>11</v>
+      <c r="D158" s="17">
+        <v>17</v>
       </c>
       <c r="G158" s="16" t="s">
         <v>269</v>
@@ -7752,8 +7759,8 @@
       <c r="H158" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I158" s="23">
-        <v>11</v>
+      <c r="I158" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="2:9">
@@ -7764,7 +7771,7 @@
         <v>480</v>
       </c>
       <c r="D159" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G159" s="16" t="s">
         <v>273</v>
@@ -7773,7 +7780,7 @@
         <v>274</v>
       </c>
       <c r="I159" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="2:9">
@@ -7783,8 +7790,8 @@
       <c r="C160" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D160" s="23">
-        <v>11</v>
+      <c r="D160" s="17">
+        <v>17</v>
       </c>
       <c r="G160" s="16" t="s">
         <v>277</v>
@@ -7792,8 +7799,8 @@
       <c r="H160" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="I160" s="23">
-        <v>11</v>
+      <c r="I160" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="2:9">
@@ -7804,7 +7811,7 @@
         <v>484</v>
       </c>
       <c r="D161" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G161" s="16" t="s">
         <v>281</v>
@@ -7813,7 +7820,7 @@
         <v>282</v>
       </c>
       <c r="I161" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="2:9">
@@ -7823,8 +7830,8 @@
       <c r="C162" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D162" s="23">
-        <v>11</v>
+      <c r="D162" s="17">
+        <v>17</v>
       </c>
       <c r="G162" s="16" t="s">
         <v>285</v>
@@ -7832,8 +7839,8 @@
       <c r="H162" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I162" s="23">
-        <v>11</v>
+      <c r="I162" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="2:9">
@@ -7844,7 +7851,7 @@
         <v>488</v>
       </c>
       <c r="D163" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G163" s="16" t="s">
         <v>289</v>
@@ -7853,7 +7860,7 @@
         <v>290</v>
       </c>
       <c r="I163" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="2:9">
@@ -7863,8 +7870,8 @@
       <c r="C164" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D164" s="23">
-        <v>11</v>
+      <c r="D164" s="17">
+        <v>17</v>
       </c>
       <c r="G164" s="16" t="s">
         <v>293</v>
@@ -7872,8 +7879,8 @@
       <c r="H164" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="I164" s="23">
-        <v>11</v>
+      <c r="I164" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="2:9">
@@ -7884,7 +7891,7 @@
         <v>492</v>
       </c>
       <c r="D165" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G165" s="24" t="s">
         <v>297</v>
@@ -7893,7 +7900,7 @@
         <v>298</v>
       </c>
       <c r="I165" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="2:9">
@@ -7903,8 +7910,8 @@
       <c r="C166" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="D166" s="14">
-        <v>12</v>
+      <c r="D166" s="17">
+        <v>18</v>
       </c>
       <c r="G166" s="12" t="s">
         <v>301</v>
@@ -7912,7 +7919,7 @@
       <c r="H166" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="I166" s="14">
+      <c r="I166" s="17">
         <v>12</v>
       </c>
     </row>
@@ -7924,7 +7931,7 @@
         <v>496</v>
       </c>
       <c r="D167" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G167" s="16" t="s">
         <v>305</v>
@@ -7943,8 +7950,8 @@
       <c r="C168" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D168" s="14">
-        <v>12</v>
+      <c r="D168" s="17">
+        <v>18</v>
       </c>
       <c r="G168" s="16" t="s">
         <v>309</v>
@@ -7952,7 +7959,7 @@
       <c r="H168" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="I168" s="14">
+      <c r="I168" s="17">
         <v>12</v>
       </c>
     </row>
@@ -7964,7 +7971,7 @@
         <v>500</v>
       </c>
       <c r="D169" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G169" s="16" t="s">
         <v>313</v>
@@ -7983,8 +7990,8 @@
       <c r="C170" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D170" s="14">
-        <v>12</v>
+      <c r="D170" s="17">
+        <v>18</v>
       </c>
       <c r="G170" s="16" t="s">
         <v>317</v>
@@ -7992,7 +7999,7 @@
       <c r="H170" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="I170" s="14">
+      <c r="I170" s="17">
         <v>12</v>
       </c>
     </row>
@@ -8004,7 +8011,7 @@
         <v>504</v>
       </c>
       <c r="D171" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G171" s="16" t="s">
         <v>321</v>
@@ -8023,8 +8030,8 @@
       <c r="C172" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D172" s="14">
-        <v>12</v>
+      <c r="D172" s="17">
+        <v>18</v>
       </c>
       <c r="G172" s="16" t="s">
         <v>325</v>
@@ -8032,7 +8039,7 @@
       <c r="H172" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I172" s="14">
+      <c r="I172" s="17">
         <v>12</v>
       </c>
     </row>
@@ -8044,7 +8051,7 @@
         <v>508</v>
       </c>
       <c r="D173" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G173" s="16" t="s">
         <v>329</v>
@@ -8063,8 +8070,8 @@
       <c r="C174" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D174" s="14">
-        <v>12</v>
+      <c r="D174" s="17">
+        <v>18</v>
       </c>
       <c r="G174" s="16" t="s">
         <v>333</v>
@@ -8072,7 +8079,7 @@
       <c r="H174" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="I174" s="14">
+      <c r="I174" s="17">
         <v>12</v>
       </c>
     </row>
@@ -8084,7 +8091,7 @@
         <v>512</v>
       </c>
       <c r="D175" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G175" s="16" t="s">
         <v>337</v>
@@ -8103,8 +8110,8 @@
       <c r="C176" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="D176" s="14">
-        <v>12</v>
+      <c r="D176" s="17">
+        <v>18</v>
       </c>
       <c r="G176" s="16" t="s">
         <v>341</v>
@@ -8112,7 +8119,7 @@
       <c r="H176" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I176" s="14">
+      <c r="I176" s="17">
         <v>12</v>
       </c>
     </row>
@@ -8124,7 +8131,7 @@
         <v>516</v>
       </c>
       <c r="D177" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G177" s="18" t="s">
         <v>345</v>
@@ -8143,8 +8150,8 @@
       <c r="C178" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="D178" s="23">
-        <v>13</v>
+      <c r="D178" s="17">
+        <v>19</v>
       </c>
       <c r="G178" s="21" t="s">
         <v>349</v>
@@ -8152,8 +8159,8 @@
       <c r="H178" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="I178" s="23">
-        <v>13</v>
+      <c r="I178" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="2:9">
@@ -8164,7 +8171,7 @@
         <v>520</v>
       </c>
       <c r="D179" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G179" s="16" t="s">
         <v>353</v>
@@ -8173,7 +8180,7 @@
         <v>354</v>
       </c>
       <c r="I179" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="2:9">
@@ -8183,8 +8190,8 @@
       <c r="C180" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D180" s="23">
-        <v>13</v>
+      <c r="D180" s="17">
+        <v>19</v>
       </c>
       <c r="G180" s="16" t="s">
         <v>357</v>
@@ -8192,8 +8199,8 @@
       <c r="H180" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="I180" s="23">
-        <v>13</v>
+      <c r="I180" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="2:9">
@@ -8204,7 +8211,7 @@
         <v>524</v>
       </c>
       <c r="D181" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G181" s="16" t="s">
         <v>361</v>
@@ -8213,7 +8220,7 @@
         <v>362</v>
       </c>
       <c r="I181" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="2:9">
@@ -8223,8 +8230,8 @@
       <c r="C182" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D182" s="23">
-        <v>13</v>
+      <c r="D182" s="17">
+        <v>19</v>
       </c>
       <c r="G182" s="16" t="s">
         <v>365</v>
@@ -8232,8 +8239,8 @@
       <c r="H182" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="I182" s="23">
-        <v>13</v>
+      <c r="I182" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="2:9">
@@ -8244,7 +8251,7 @@
         <v>528</v>
       </c>
       <c r="D183" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G183" s="16" t="s">
         <v>369</v>
@@ -8253,7 +8260,7 @@
         <v>370</v>
       </c>
       <c r="I183" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="2:9">
@@ -8263,8 +8270,8 @@
       <c r="C184" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D184" s="23">
-        <v>13</v>
+      <c r="D184" s="17">
+        <v>19</v>
       </c>
       <c r="G184" s="16" t="s">
         <v>373</v>
@@ -8272,8 +8279,8 @@
       <c r="H184" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="I184" s="23">
-        <v>13</v>
+      <c r="I184" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="2:9">
@@ -8284,7 +8291,7 @@
         <v>532</v>
       </c>
       <c r="D185" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G185" s="16" t="s">
         <v>377</v>
@@ -8293,7 +8300,7 @@
         <v>378</v>
       </c>
       <c r="I185" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="2:9">
@@ -8303,8 +8310,8 @@
       <c r="C186" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D186" s="23">
-        <v>13</v>
+      <c r="D186" s="17">
+        <v>19</v>
       </c>
       <c r="G186" s="16" t="s">
         <v>381</v>
@@ -8312,8 +8319,8 @@
       <c r="H186" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="I186" s="23">
-        <v>13</v>
+      <c r="I186" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="2:9">
@@ -8324,7 +8331,7 @@
         <v>536</v>
       </c>
       <c r="D187" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G187" s="16" t="s">
         <v>385</v>
@@ -8333,7 +8340,7 @@
         <v>386</v>
       </c>
       <c r="I187" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="2:9">
@@ -8343,8 +8350,8 @@
       <c r="C188" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D188" s="23">
-        <v>13</v>
+      <c r="D188" s="17">
+        <v>19</v>
       </c>
       <c r="G188" s="16" t="s">
         <v>389</v>
@@ -8352,8 +8359,8 @@
       <c r="H188" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I188" s="23">
-        <v>13</v>
+      <c r="I188" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="2:9">
@@ -8364,7 +8371,7 @@
         <v>540</v>
       </c>
       <c r="D189" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G189" s="16" t="s">
         <v>393</v>
@@ -8373,7 +8380,7 @@
         <v>394</v>
       </c>
       <c r="I189" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="2:9">
@@ -8383,8 +8390,8 @@
       <c r="C190" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D190" s="23">
-        <v>13</v>
+      <c r="D190" s="17">
+        <v>19</v>
       </c>
       <c r="G190" s="16" t="s">
         <v>397</v>
@@ -8392,8 +8399,8 @@
       <c r="H190" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="I190" s="23">
-        <v>13</v>
+      <c r="I190" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="2:9">
@@ -8404,7 +8411,7 @@
         <v>544</v>
       </c>
       <c r="D191" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G191" s="16" t="s">
         <v>401</v>
@@ -8413,7 +8420,7 @@
         <v>402</v>
       </c>
       <c r="I191" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="2:9">
@@ -8423,8 +8430,8 @@
       <c r="C192" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D192" s="23">
-        <v>13</v>
+      <c r="D192" s="17">
+        <v>19</v>
       </c>
       <c r="G192" s="16" t="s">
         <v>405</v>
@@ -8432,8 +8439,8 @@
       <c r="H192" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="I192" s="23">
-        <v>13</v>
+      <c r="I192" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="2:9">
@@ -8444,7 +8451,7 @@
         <v>548</v>
       </c>
       <c r="D193" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G193" s="16" t="s">
         <v>409</v>
@@ -8453,7 +8460,7 @@
         <v>410</v>
       </c>
       <c r="I193" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="2:9">
@@ -8463,8 +8470,8 @@
       <c r="C194" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D194" s="23">
-        <v>13</v>
+      <c r="D194" s="17">
+        <v>19</v>
       </c>
       <c r="G194" s="16" t="s">
         <v>413</v>
@@ -8472,8 +8479,8 @@
       <c r="H194" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="I194" s="23">
-        <v>13</v>
+      <c r="I194" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="2:9">
@@ -8484,7 +8491,7 @@
         <v>552</v>
       </c>
       <c r="D195" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G195" s="16" t="s">
         <v>417</v>
@@ -8493,7 +8500,7 @@
         <v>418</v>
       </c>
       <c r="I195" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="2:9">
@@ -8503,8 +8510,8 @@
       <c r="C196" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D196" s="23">
-        <v>13</v>
+      <c r="D196" s="17">
+        <v>19</v>
       </c>
       <c r="G196" s="16" t="s">
         <v>421</v>
@@ -8512,8 +8519,8 @@
       <c r="H196" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="I196" s="23">
-        <v>13</v>
+      <c r="I196" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="2:9">
@@ -8524,7 +8531,7 @@
         <v>556</v>
       </c>
       <c r="D197" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G197" s="24" t="s">
         <v>425</v>
@@ -8533,7 +8540,7 @@
         <v>426</v>
       </c>
       <c r="I197" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="2:9">
@@ -8543,8 +8550,8 @@
       <c r="C198" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="D198" s="14">
-        <v>14</v>
+      <c r="D198" s="17">
+        <v>20</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>559</v>
@@ -8552,8 +8559,8 @@
       <c r="H198" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="I198" s="14">
-        <v>14</v>
+      <c r="I198" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="2:9">
@@ -8564,7 +8571,7 @@
         <v>561</v>
       </c>
       <c r="D199" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G199" s="16" t="s">
         <v>562</v>
@@ -8573,7 +8580,7 @@
         <v>432</v>
       </c>
       <c r="I199" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="2:9">
@@ -8583,8 +8590,8 @@
       <c r="C200" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="D200" s="14">
-        <v>14</v>
+      <c r="D200" s="17">
+        <v>20</v>
       </c>
       <c r="G200" s="16" t="s">
         <v>565</v>
@@ -8592,8 +8599,8 @@
       <c r="H200" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="I200" s="14">
-        <v>14</v>
+      <c r="I200" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="2:9">
@@ -8604,7 +8611,7 @@
         <v>567</v>
       </c>
       <c r="D201" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G201" s="16" t="s">
         <v>568</v>
@@ -8613,7 +8620,7 @@
         <v>436</v>
       </c>
       <c r="I201" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="2:9">
@@ -8623,8 +8630,8 @@
       <c r="C202" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D202" s="14">
-        <v>14</v>
+      <c r="D202" s="17">
+        <v>20</v>
       </c>
       <c r="G202" s="16" t="s">
         <v>571</v>
@@ -8632,8 +8639,8 @@
       <c r="H202" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="I202" s="14">
-        <v>14</v>
+      <c r="I202" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="2:9">
@@ -8644,7 +8651,7 @@
         <v>573</v>
       </c>
       <c r="D203" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G203" s="16" t="s">
         <v>574</v>
@@ -8653,7 +8660,7 @@
         <v>440</v>
       </c>
       <c r="I203" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="2:9">
@@ -8663,8 +8670,8 @@
       <c r="C204" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D204" s="14">
-        <v>14</v>
+      <c r="D204" s="17">
+        <v>20</v>
       </c>
       <c r="G204" s="16" t="s">
         <v>577</v>
@@ -8672,8 +8679,8 @@
       <c r="H204" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="I204" s="14">
-        <v>14</v>
+      <c r="I204" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="2:9">
@@ -8684,7 +8691,7 @@
         <v>579</v>
       </c>
       <c r="D205" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G205" s="16" t="s">
         <v>580</v>
@@ -8693,7 +8700,7 @@
         <v>444</v>
       </c>
       <c r="I205" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="2:9">
@@ -8703,8 +8710,8 @@
       <c r="C206" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="D206" s="14">
-        <v>14</v>
+      <c r="D206" s="17">
+        <v>20</v>
       </c>
       <c r="G206" s="16" t="s">
         <v>583</v>
@@ -8712,8 +8719,8 @@
       <c r="H206" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="I206" s="14">
-        <v>14</v>
+      <c r="I206" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="2:9">
@@ -8724,7 +8731,7 @@
         <v>585</v>
       </c>
       <c r="D207" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G207" s="16" t="s">
         <v>586</v>
@@ -8733,7 +8740,7 @@
         <v>448</v>
       </c>
       <c r="I207" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="2:9">
@@ -8743,8 +8750,8 @@
       <c r="C208" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D208" s="14">
-        <v>14</v>
+      <c r="D208" s="17">
+        <v>20</v>
       </c>
       <c r="G208" s="16" t="s">
         <v>589</v>
@@ -8752,8 +8759,8 @@
       <c r="H208" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="I208" s="14">
-        <v>14</v>
+      <c r="I208" s="17">
+        <v>21</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="2:9">
@@ -8764,7 +8771,7 @@
         <v>591</v>
       </c>
       <c r="D209" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G209" s="18" t="s">
         <v>592</v>
@@ -8773,7 +8780,7 @@
         <v>452</v>
       </c>
       <c r="I209" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="2:9">
@@ -8783,8 +8790,8 @@
       <c r="C210" s="22" t="s">
         <v>594</v>
       </c>
-      <c r="D210" s="23">
-        <v>15</v>
+      <c r="D210" s="17">
+        <v>22</v>
       </c>
       <c r="G210" s="21" t="s">
         <v>453</v>
@@ -8792,8 +8799,8 @@
       <c r="H210" s="22" t="s">
         <v>595</v>
       </c>
-      <c r="I210" s="23">
-        <v>15</v>
+      <c r="I210" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="2:9">
@@ -8804,7 +8811,7 @@
         <v>597</v>
       </c>
       <c r="D211" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G211" s="16" t="s">
         <v>455</v>
@@ -8813,7 +8820,7 @@
         <v>598</v>
       </c>
       <c r="I211" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="2:9">
@@ -8823,8 +8830,8 @@
       <c r="C212" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="D212" s="23">
-        <v>15</v>
+      <c r="D212" s="17">
+        <v>22</v>
       </c>
       <c r="G212" s="16" t="s">
         <v>457</v>
@@ -8832,8 +8839,8 @@
       <c r="H212" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="I212" s="23">
-        <v>15</v>
+      <c r="I212" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="2:9">
@@ -8844,7 +8851,7 @@
         <v>603</v>
       </c>
       <c r="D213" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G213" s="16" t="s">
         <v>459</v>
@@ -8853,7 +8860,7 @@
         <v>604</v>
       </c>
       <c r="I213" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="2:9">
@@ -8863,8 +8870,8 @@
       <c r="C214" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="D214" s="23">
-        <v>15</v>
+      <c r="D214" s="17">
+        <v>22</v>
       </c>
       <c r="G214" s="16" t="s">
         <v>461</v>
@@ -8872,8 +8879,8 @@
       <c r="H214" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="I214" s="23">
-        <v>15</v>
+      <c r="I214" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="2:9">
@@ -8884,7 +8891,7 @@
         <v>609</v>
       </c>
       <c r="D215" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G215" s="16" t="s">
         <v>463</v>
@@ -8893,7 +8900,7 @@
         <v>610</v>
       </c>
       <c r="I215" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="2:9">
@@ -8903,8 +8910,8 @@
       <c r="C216" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="D216" s="23">
-        <v>15</v>
+      <c r="D216" s="17">
+        <v>22</v>
       </c>
       <c r="G216" s="16" t="s">
         <v>465</v>
@@ -8912,8 +8919,8 @@
       <c r="H216" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="I216" s="23">
-        <v>15</v>
+      <c r="I216" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="2:9">
@@ -8924,7 +8931,7 @@
         <v>615</v>
       </c>
       <c r="D217" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G217" s="16" t="s">
         <v>467</v>
@@ -8933,7 +8940,7 @@
         <v>616</v>
       </c>
       <c r="I217" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="2:9">
@@ -8943,8 +8950,8 @@
       <c r="C218" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D218" s="23">
-        <v>15</v>
+      <c r="D218" s="17">
+        <v>22</v>
       </c>
       <c r="G218" s="16" t="s">
         <v>469</v>
@@ -8952,8 +8959,8 @@
       <c r="H218" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="I218" s="23">
-        <v>15</v>
+      <c r="I218" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="2:9">
@@ -8964,7 +8971,7 @@
         <v>621</v>
       </c>
       <c r="D219" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G219" s="16" t="s">
         <v>471</v>
@@ -8973,7 +8980,7 @@
         <v>622</v>
       </c>
       <c r="I219" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="2:9">
@@ -8983,8 +8990,8 @@
       <c r="C220" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="D220" s="23">
-        <v>15</v>
+      <c r="D220" s="17">
+        <v>22</v>
       </c>
       <c r="G220" s="16" t="s">
         <v>473</v>
@@ -8992,8 +8999,8 @@
       <c r="H220" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="I220" s="23">
-        <v>15</v>
+      <c r="I220" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="2:9">
@@ -9004,7 +9011,7 @@
         <v>627</v>
       </c>
       <c r="D221" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G221" s="16" t="s">
         <v>475</v>
@@ -9013,7 +9020,7 @@
         <v>628</v>
       </c>
       <c r="I221" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="2:9">
@@ -9023,8 +9030,8 @@
       <c r="C222" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D222" s="23">
-        <v>15</v>
+      <c r="D222" s="17">
+        <v>22</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>477</v>
@@ -9032,8 +9039,8 @@
       <c r="H222" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="I222" s="23">
-        <v>15</v>
+      <c r="I222" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="2:9">
@@ -9044,7 +9051,7 @@
         <v>633</v>
       </c>
       <c r="D223" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G223" s="16" t="s">
         <v>479</v>
@@ -9053,7 +9060,7 @@
         <v>634</v>
       </c>
       <c r="I223" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="2:9">
@@ -9063,8 +9070,8 @@
       <c r="C224" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="D224" s="23">
-        <v>15</v>
+      <c r="D224" s="17">
+        <v>22</v>
       </c>
       <c r="G224" s="16" t="s">
         <v>481</v>
@@ -9072,8 +9079,8 @@
       <c r="H224" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="I224" s="23">
-        <v>15</v>
+      <c r="I224" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="2:9">
@@ -9084,7 +9091,7 @@
         <v>639</v>
       </c>
       <c r="D225" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G225" s="16" t="s">
         <v>483</v>
@@ -9093,7 +9100,7 @@
         <v>640</v>
       </c>
       <c r="I225" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="2:9">
@@ -9103,8 +9110,8 @@
       <c r="C226" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="D226" s="23">
-        <v>15</v>
+      <c r="D226" s="17">
+        <v>22</v>
       </c>
       <c r="G226" s="16" t="s">
         <v>485</v>
@@ -9112,8 +9119,8 @@
       <c r="H226" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="I226" s="23">
-        <v>15</v>
+      <c r="I226" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="2:9">
@@ -9124,7 +9131,7 @@
         <v>645</v>
       </c>
       <c r="D227" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G227" s="16" t="s">
         <v>487</v>
@@ -9133,7 +9140,7 @@
         <v>646</v>
       </c>
       <c r="I227" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="2:9">
@@ -9143,8 +9150,8 @@
       <c r="C228" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D228" s="23">
-        <v>15</v>
+      <c r="D228" s="17">
+        <v>22</v>
       </c>
       <c r="G228" s="16" t="s">
         <v>489</v>
@@ -9152,8 +9159,8 @@
       <c r="H228" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="I228" s="23">
-        <v>15</v>
+      <c r="I228" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="2:9">
@@ -9164,7 +9171,7 @@
         <v>651</v>
       </c>
       <c r="D229" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G229" s="24" t="s">
         <v>491</v>
@@ -9173,7 +9180,7 @@
         <v>652</v>
       </c>
       <c r="I229" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="2:9">
@@ -9183,8 +9190,8 @@
       <c r="C230" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="D230" s="14">
-        <v>16</v>
+      <c r="D230" s="17">
+        <v>24</v>
       </c>
       <c r="G230" s="12" t="s">
         <v>77</v>
@@ -9192,8 +9199,8 @@
       <c r="H230" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="I230" s="14">
-        <v>16</v>
+      <c r="I230" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="2:9">
@@ -9204,7 +9211,7 @@
         <v>657</v>
       </c>
       <c r="D231" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G231" s="16" t="s">
         <v>80</v>
@@ -9213,7 +9220,7 @@
         <v>658</v>
       </c>
       <c r="I231" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="2:9">
@@ -9223,8 +9230,8 @@
       <c r="C232" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="D232" s="14">
-        <v>16</v>
+      <c r="D232" s="17">
+        <v>24</v>
       </c>
       <c r="G232" s="16" t="s">
         <v>83</v>
@@ -9232,8 +9239,8 @@
       <c r="H232" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="I232" s="14">
-        <v>16</v>
+      <c r="I232" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="2:9">
@@ -9244,7 +9251,7 @@
         <v>663</v>
       </c>
       <c r="D233" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G233" s="16" t="s">
         <v>86</v>
@@ -9253,7 +9260,7 @@
         <v>664</v>
       </c>
       <c r="I233" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="2:9">
@@ -9263,8 +9270,8 @@
       <c r="C234" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D234" s="14">
-        <v>16</v>
+      <c r="D234" s="17">
+        <v>24</v>
       </c>
       <c r="G234" s="16" t="s">
         <v>89</v>
@@ -9272,8 +9279,8 @@
       <c r="H234" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="I234" s="14">
-        <v>16</v>
+      <c r="I234" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="2:9">
@@ -9284,7 +9291,7 @@
         <v>669</v>
       </c>
       <c r="D235" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G235" s="16" t="s">
         <v>92</v>
@@ -9293,7 +9300,7 @@
         <v>670</v>
       </c>
       <c r="I235" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="2:9">
@@ -9303,8 +9310,8 @@
       <c r="C236" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="D236" s="14">
-        <v>16</v>
+      <c r="D236" s="17">
+        <v>24</v>
       </c>
       <c r="G236" s="16" t="s">
         <v>95</v>
@@ -9312,8 +9319,8 @@
       <c r="H236" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="I236" s="14">
-        <v>16</v>
+      <c r="I236" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="2:9">
@@ -9324,7 +9331,7 @@
         <v>675</v>
       </c>
       <c r="D237" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G237" s="16" t="s">
         <v>98</v>
@@ -9333,7 +9340,7 @@
         <v>676</v>
       </c>
       <c r="I237" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="2:9">
@@ -9343,8 +9350,8 @@
       <c r="C238" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="D238" s="14">
-        <v>16</v>
+      <c r="D238" s="17">
+        <v>24</v>
       </c>
       <c r="G238" s="16" t="s">
         <v>101</v>
@@ -9352,8 +9359,8 @@
       <c r="H238" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="I238" s="14">
-        <v>16</v>
+      <c r="I238" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="2:9">
@@ -9364,7 +9371,7 @@
         <v>681</v>
       </c>
       <c r="D239" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G239" s="16" t="s">
         <v>104</v>
@@ -9373,7 +9380,7 @@
         <v>682</v>
       </c>
       <c r="I239" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="2:9">
@@ -9383,8 +9390,8 @@
       <c r="C240" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D240" s="14">
-        <v>16</v>
+      <c r="D240" s="17">
+        <v>24</v>
       </c>
       <c r="G240" s="16" t="s">
         <v>107</v>
@@ -9392,8 +9399,8 @@
       <c r="H240" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="I240" s="14">
-        <v>16</v>
+      <c r="I240" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="2:9">
@@ -9404,7 +9411,7 @@
         <v>687</v>
       </c>
       <c r="D241" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G241" s="18" t="s">
         <v>110</v>
@@ -9413,7 +9420,7 @@
         <v>688</v>
       </c>
       <c r="I241" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1" spans="2:9">
@@ -9423,8 +9430,8 @@
       <c r="C242" s="22" t="s">
         <v>690</v>
       </c>
-      <c r="D242" s="23">
-        <v>17</v>
+      <c r="D242" s="17">
+        <v>26</v>
       </c>
       <c r="G242" s="21" t="s">
         <v>691</v>
@@ -9432,8 +9439,8 @@
       <c r="H242" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="I242" s="23">
-        <v>17</v>
+      <c r="I242" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1" spans="2:9">
@@ -9444,7 +9451,7 @@
         <v>693</v>
       </c>
       <c r="D243" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G243" s="16" t="s">
         <v>694</v>
@@ -9453,7 +9460,7 @@
         <v>117</v>
       </c>
       <c r="I243" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1" spans="2:9">
@@ -9463,8 +9470,8 @@
       <c r="C244" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D244" s="23">
-        <v>17</v>
+      <c r="D244" s="17">
+        <v>26</v>
       </c>
       <c r="G244" s="16" t="s">
         <v>697</v>
@@ -9472,8 +9479,8 @@
       <c r="H244" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I244" s="23">
-        <v>17</v>
+      <c r="I244" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="2:9">
@@ -9484,7 +9491,7 @@
         <v>699</v>
       </c>
       <c r="D245" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G245" s="16" t="s">
         <v>700</v>
@@ -9493,7 +9500,7 @@
         <v>123</v>
       </c>
       <c r="I245" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="2:9">
@@ -9503,8 +9510,8 @@
       <c r="C246" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="D246" s="23">
-        <v>17</v>
+      <c r="D246" s="17">
+        <v>26</v>
       </c>
       <c r="G246" s="16" t="s">
         <v>703</v>
@@ -9512,8 +9519,8 @@
       <c r="H246" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I246" s="23">
-        <v>17</v>
+      <c r="I246" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="2:9">
@@ -9524,7 +9531,7 @@
         <v>705</v>
       </c>
       <c r="D247" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G247" s="16" t="s">
         <v>706</v>
@@ -9533,7 +9540,7 @@
         <v>129</v>
       </c>
       <c r="I247" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="2:9">
@@ -9543,8 +9550,8 @@
       <c r="C248" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="D248" s="23">
-        <v>17</v>
+      <c r="D248" s="17">
+        <v>26</v>
       </c>
       <c r="G248" s="16" t="s">
         <v>709</v>
@@ -9552,8 +9559,8 @@
       <c r="H248" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I248" s="23">
-        <v>17</v>
+      <c r="I248" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="2:9">
@@ -9564,7 +9571,7 @@
         <v>711</v>
       </c>
       <c r="D249" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G249" s="16" t="s">
         <v>712</v>
@@ -9573,7 +9580,7 @@
         <v>135</v>
       </c>
       <c r="I249" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="2:9">
@@ -9583,8 +9590,8 @@
       <c r="C250" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="D250" s="23">
-        <v>17</v>
+      <c r="D250" s="17">
+        <v>26</v>
       </c>
       <c r="G250" s="16" t="s">
         <v>715</v>
@@ -9592,8 +9599,8 @@
       <c r="H250" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="I250" s="23">
-        <v>17</v>
+      <c r="I250" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1" spans="2:9">
@@ -9604,7 +9611,7 @@
         <v>717</v>
       </c>
       <c r="D251" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G251" s="16" t="s">
         <v>718</v>
@@ -9613,7 +9620,7 @@
         <v>141</v>
       </c>
       <c r="I251" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1" spans="2:9">
@@ -9623,8 +9630,8 @@
       <c r="C252" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="D252" s="23">
-        <v>17</v>
+      <c r="D252" s="17">
+        <v>26</v>
       </c>
       <c r="G252" s="16" t="s">
         <v>721</v>
@@ -9632,8 +9639,8 @@
       <c r="H252" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I252" s="23">
-        <v>17</v>
+      <c r="I252" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="2:9">
@@ -9644,7 +9651,7 @@
         <v>723</v>
       </c>
       <c r="D253" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G253" s="16" t="s">
         <v>724</v>
@@ -9653,7 +9660,7 @@
         <v>147</v>
       </c>
       <c r="I253" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="2:9">
@@ -9663,8 +9670,8 @@
       <c r="C254" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="D254" s="23">
-        <v>17</v>
+      <c r="D254" s="17">
+        <v>26</v>
       </c>
       <c r="G254" s="16" t="s">
         <v>727</v>
@@ -9672,8 +9679,8 @@
       <c r="H254" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I254" s="23">
-        <v>17</v>
+      <c r="I254" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="2:9">
@@ -9684,7 +9691,7 @@
         <v>729</v>
       </c>
       <c r="D255" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G255" s="16" t="s">
         <v>730</v>
@@ -9693,7 +9700,7 @@
         <v>153</v>
       </c>
       <c r="I255" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="2:9">
@@ -9703,8 +9710,8 @@
       <c r="C256" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D256" s="23">
-        <v>17</v>
+      <c r="D256" s="17">
+        <v>26</v>
       </c>
       <c r="G256" s="16" t="s">
         <v>733</v>
@@ -9712,8 +9719,8 @@
       <c r="H256" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I256" s="23">
-        <v>17</v>
+      <c r="I256" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1" spans="2:9">
@@ -9724,7 +9731,7 @@
         <v>735</v>
       </c>
       <c r="D257" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G257" s="16" t="s">
         <v>736</v>
@@ -9733,7 +9740,7 @@
         <v>159</v>
       </c>
       <c r="I257" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1" spans="2:9">
@@ -9743,8 +9750,8 @@
       <c r="C258" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="D258" s="23">
-        <v>17</v>
+      <c r="D258" s="17">
+        <v>26</v>
       </c>
       <c r="G258" s="16" t="s">
         <v>739</v>
@@ -9752,8 +9759,8 @@
       <c r="H258" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I258" s="23">
-        <v>17</v>
+      <c r="I258" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1" spans="2:9">
@@ -9764,7 +9771,7 @@
         <v>741</v>
       </c>
       <c r="D259" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G259" s="16" t="s">
         <v>742</v>
@@ -9773,7 +9780,7 @@
         <v>165</v>
       </c>
       <c r="I259" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" spans="2:9">
@@ -9783,8 +9790,8 @@
       <c r="C260" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D260" s="23">
-        <v>17</v>
+      <c r="D260" s="17">
+        <v>26</v>
       </c>
       <c r="G260" s="16" t="s">
         <v>745</v>
@@ -9792,8 +9799,8 @@
       <c r="H260" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="I260" s="23">
-        <v>17</v>
+      <c r="I260" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" spans="2:9">
@@ -9804,7 +9811,7 @@
         <v>747</v>
       </c>
       <c r="D261" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G261" s="24" t="s">
         <v>748</v>
@@ -9813,7 +9820,7 @@
         <v>171</v>
       </c>
       <c r="I261" s="17">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" spans="2:9">
@@ -9823,8 +9830,8 @@
       <c r="C262" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="D262" s="14">
-        <v>18</v>
+      <c r="D262" s="17">
+        <v>28</v>
       </c>
       <c r="G262" s="15" t="s">
         <v>429</v>
@@ -9832,8 +9839,8 @@
       <c r="H262" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="I262" s="14">
-        <v>18</v>
+      <c r="I262" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" spans="2:9">
@@ -9844,7 +9851,7 @@
         <v>753</v>
       </c>
       <c r="D263" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G263" s="16" t="s">
         <v>431</v>
@@ -9853,7 +9860,7 @@
         <v>754</v>
       </c>
       <c r="I263" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="2:9">
@@ -9863,8 +9870,8 @@
       <c r="C264" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="D264" s="14">
-        <v>18</v>
+      <c r="D264" s="17">
+        <v>28</v>
       </c>
       <c r="G264" s="16" t="s">
         <v>433</v>
@@ -9872,8 +9879,8 @@
       <c r="H264" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="I264" s="14">
-        <v>18</v>
+      <c r="I264" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="2:9">
@@ -9884,7 +9891,7 @@
         <v>759</v>
       </c>
       <c r="D265" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G265" s="16" t="s">
         <v>435</v>
@@ -9893,7 +9900,7 @@
         <v>760</v>
       </c>
       <c r="I265" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="2:9">
@@ -9903,8 +9910,8 @@
       <c r="C266" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D266" s="14">
-        <v>18</v>
+      <c r="D266" s="17">
+        <v>28</v>
       </c>
       <c r="G266" s="16" t="s">
         <v>437</v>
@@ -9912,8 +9919,8 @@
       <c r="H266" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="I266" s="14">
-        <v>18</v>
+      <c r="I266" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="2:9">
@@ -9924,7 +9931,7 @@
         <v>765</v>
       </c>
       <c r="D267" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G267" s="16" t="s">
         <v>439</v>
@@ -9933,7 +9940,7 @@
         <v>766</v>
       </c>
       <c r="I267" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1" spans="2:9">
@@ -9943,8 +9950,8 @@
       <c r="C268" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D268" s="14">
-        <v>18</v>
+      <c r="D268" s="17">
+        <v>28</v>
       </c>
       <c r="G268" s="16" t="s">
         <v>441</v>
@@ -9952,8 +9959,8 @@
       <c r="H268" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="I268" s="14">
-        <v>18</v>
+      <c r="I268" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1" spans="2:9">
@@ -9964,7 +9971,7 @@
         <v>771</v>
       </c>
       <c r="D269" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G269" s="16" t="s">
         <v>443</v>
@@ -9973,7 +9980,7 @@
         <v>772</v>
       </c>
       <c r="I269" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1" spans="2:9">
@@ -9983,8 +9990,8 @@
       <c r="C270" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D270" s="14">
-        <v>18</v>
+      <c r="D270" s="17">
+        <v>28</v>
       </c>
       <c r="G270" s="16" t="s">
         <v>445</v>
@@ -9992,8 +9999,8 @@
       <c r="H270" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="I270" s="14">
-        <v>18</v>
+      <c r="I270" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1" spans="2:9">
@@ -10004,7 +10011,7 @@
         <v>777</v>
       </c>
       <c r="D271" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G271" s="16" t="s">
         <v>447</v>
@@ -10013,7 +10020,7 @@
         <v>778</v>
       </c>
       <c r="I271" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" spans="2:9">
@@ -10023,8 +10030,8 @@
       <c r="C272" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="D272" s="14">
-        <v>18</v>
+      <c r="D272" s="17">
+        <v>28</v>
       </c>
       <c r="G272" s="16" t="s">
         <v>449</v>
@@ -10032,8 +10039,8 @@
       <c r="H272" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="I272" s="14">
-        <v>18</v>
+      <c r="I272" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1" spans="2:9">
@@ -10044,7 +10051,7 @@
         <v>783</v>
       </c>
       <c r="D273" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G273" s="18" t="s">
         <v>451</v>
@@ -10053,7 +10060,7 @@
         <v>784</v>
       </c>
       <c r="I273" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1" spans="2:9">
@@ -10063,8 +10070,8 @@
       <c r="C274" s="22" t="s">
         <v>786</v>
       </c>
-      <c r="D274" s="23">
-        <v>19</v>
+      <c r="D274" s="17">
+        <v>30</v>
       </c>
       <c r="G274" s="21" t="s">
         <v>787</v>
@@ -10072,8 +10079,8 @@
       <c r="H274" s="22" t="s">
         <v>454</v>
       </c>
-      <c r="I274" s="23">
-        <v>19</v>
+      <c r="I274" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1" spans="2:9">
@@ -10084,7 +10091,7 @@
         <v>789</v>
       </c>
       <c r="D275" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G275" s="16" t="s">
         <v>790</v>
@@ -10093,7 +10100,7 @@
         <v>456</v>
       </c>
       <c r="I275" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" spans="2:9">
@@ -10103,8 +10110,8 @@
       <c r="C276" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D276" s="23">
-        <v>19</v>
+      <c r="D276" s="17">
+        <v>30</v>
       </c>
       <c r="G276" s="16" t="s">
         <v>793</v>
@@ -10112,8 +10119,8 @@
       <c r="H276" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="I276" s="23">
-        <v>19</v>
+      <c r="I276" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1" spans="2:9">
@@ -10124,7 +10131,7 @@
         <v>795</v>
       </c>
       <c r="D277" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G277" s="16" t="s">
         <v>796</v>
@@ -10133,7 +10140,7 @@
         <v>460</v>
       </c>
       <c r="I277" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1" spans="2:9">
@@ -10143,8 +10150,8 @@
       <c r="C278" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="D278" s="23">
-        <v>19</v>
+      <c r="D278" s="17">
+        <v>30</v>
       </c>
       <c r="G278" s="16" t="s">
         <v>799</v>
@@ -10152,8 +10159,8 @@
       <c r="H278" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="I278" s="23">
-        <v>19</v>
+      <c r="I278" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1" spans="2:9">
@@ -10164,7 +10171,7 @@
         <v>801</v>
       </c>
       <c r="D279" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G279" s="16" t="s">
         <v>802</v>
@@ -10173,7 +10180,7 @@
         <v>464</v>
       </c>
       <c r="I279" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1" spans="2:9">
@@ -10183,8 +10190,8 @@
       <c r="C280" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="D280" s="23">
-        <v>19</v>
+      <c r="D280" s="17">
+        <v>30</v>
       </c>
       <c r="G280" s="16" t="s">
         <v>805</v>
@@ -10192,8 +10199,8 @@
       <c r="H280" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="I280" s="23">
-        <v>19</v>
+      <c r="I280" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="281" ht="15" customHeight="1" spans="2:9">
@@ -10204,7 +10211,7 @@
         <v>807</v>
       </c>
       <c r="D281" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G281" s="16" t="s">
         <v>808</v>
@@ -10213,7 +10220,7 @@
         <v>468</v>
       </c>
       <c r="I281" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1" spans="2:9">
@@ -10223,8 +10230,8 @@
       <c r="C282" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="D282" s="23">
-        <v>19</v>
+      <c r="D282" s="17">
+        <v>30</v>
       </c>
       <c r="G282" s="16" t="s">
         <v>811</v>
@@ -10232,8 +10239,8 @@
       <c r="H282" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="I282" s="23">
-        <v>19</v>
+      <c r="I282" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1" spans="2:9">
@@ -10244,7 +10251,7 @@
         <v>813</v>
       </c>
       <c r="D283" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G283" s="16" t="s">
         <v>814</v>
@@ -10253,7 +10260,7 @@
         <v>472</v>
       </c>
       <c r="I283" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1" spans="2:9">
@@ -10263,8 +10270,8 @@
       <c r="C284" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="D284" s="23">
-        <v>19</v>
+      <c r="D284" s="17">
+        <v>30</v>
       </c>
       <c r="G284" s="16" t="s">
         <v>817</v>
@@ -10272,8 +10279,8 @@
       <c r="H284" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I284" s="23">
-        <v>19</v>
+      <c r="I284" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1" spans="2:9">
@@ -10284,7 +10291,7 @@
         <v>819</v>
       </c>
       <c r="D285" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G285" s="16" t="s">
         <v>820</v>
@@ -10293,7 +10300,7 @@
         <v>476</v>
       </c>
       <c r="I285" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1" spans="2:9">
@@ -10303,8 +10310,8 @@
       <c r="C286" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="D286" s="23">
-        <v>19</v>
+      <c r="D286" s="17">
+        <v>30</v>
       </c>
       <c r="G286" s="16" t="s">
         <v>823</v>
@@ -10312,8 +10319,8 @@
       <c r="H286" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="I286" s="23">
-        <v>19</v>
+      <c r="I286" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="287" ht="15" customHeight="1" spans="2:9">
@@ -10324,7 +10331,7 @@
         <v>825</v>
       </c>
       <c r="D287" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G287" s="16" t="s">
         <v>826</v>
@@ -10333,7 +10340,7 @@
         <v>480</v>
       </c>
       <c r="I287" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1" spans="2:9">
@@ -10343,8 +10350,8 @@
       <c r="C288" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="D288" s="23">
-        <v>19</v>
+      <c r="D288" s="17">
+        <v>30</v>
       </c>
       <c r="G288" s="16" t="s">
         <v>829</v>
@@ -10352,8 +10359,8 @@
       <c r="H288" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="I288" s="23">
-        <v>19</v>
+      <c r="I288" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1" spans="2:9">
@@ -10364,7 +10371,7 @@
         <v>831</v>
       </c>
       <c r="D289" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G289" s="16" t="s">
         <v>832</v>
@@ -10373,7 +10380,7 @@
         <v>484</v>
       </c>
       <c r="I289" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1" spans="2:9">
@@ -10383,8 +10390,8 @@
       <c r="C290" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="D290" s="23">
-        <v>19</v>
+      <c r="D290" s="17">
+        <v>30</v>
       </c>
       <c r="G290" s="16" t="s">
         <v>835</v>
@@ -10392,8 +10399,8 @@
       <c r="H290" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I290" s="23">
-        <v>19</v>
+      <c r="I290" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1" spans="2:9">
@@ -10404,7 +10411,7 @@
         <v>837</v>
       </c>
       <c r="D291" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>838</v>
@@ -10413,7 +10420,7 @@
         <v>488</v>
       </c>
       <c r="I291" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1" spans="2:9">
@@ -10423,8 +10430,8 @@
       <c r="C292" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="D292" s="23">
-        <v>19</v>
+      <c r="D292" s="17">
+        <v>30</v>
       </c>
       <c r="G292" s="16" t="s">
         <v>841</v>
@@ -10432,8 +10439,8 @@
       <c r="H292" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="I292" s="23">
-        <v>19</v>
+      <c r="I292" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1" spans="2:9">
@@ -10444,7 +10451,7 @@
         <v>843</v>
       </c>
       <c r="D293" s="17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G293" s="24" t="s">
         <v>844</v>
@@ -10453,7 +10460,7 @@
         <v>492</v>
       </c>
       <c r="I293" s="17">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="294" ht="15" customHeight="1" spans="2:9">
@@ -10463,8 +10470,8 @@
       <c r="C294" s="13" t="s">
         <v>846</v>
       </c>
-      <c r="D294" s="14">
-        <v>20</v>
+      <c r="D294" s="17">
+        <v>32</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>493</v>
@@ -10472,8 +10479,8 @@
       <c r="H294" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="I294" s="14">
-        <v>20</v>
+      <c r="I294" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1" spans="2:9">
@@ -10484,7 +10491,7 @@
         <v>848</v>
       </c>
       <c r="D295" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G295" s="16" t="s">
         <v>495</v>
@@ -10493,7 +10500,7 @@
         <v>496</v>
       </c>
       <c r="I295" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="296" ht="15" customHeight="1" spans="2:9">
@@ -10503,8 +10510,8 @@
       <c r="C296" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="D296" s="14">
-        <v>20</v>
+      <c r="D296" s="17">
+        <v>32</v>
       </c>
       <c r="G296" s="16" t="s">
         <v>497</v>
@@ -10512,8 +10519,8 @@
       <c r="H296" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="I296" s="14">
-        <v>20</v>
+      <c r="I296" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1" spans="2:9">
@@ -10524,7 +10531,7 @@
         <v>852</v>
       </c>
       <c r="D297" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G297" s="16" t="s">
         <v>499</v>
@@ -10533,7 +10540,7 @@
         <v>500</v>
       </c>
       <c r="I297" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" spans="2:9">
@@ -10543,8 +10550,8 @@
       <c r="C298" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="D298" s="14">
-        <v>20</v>
+      <c r="D298" s="17">
+        <v>32</v>
       </c>
       <c r="G298" s="16" t="s">
         <v>501</v>
@@ -10552,8 +10559,8 @@
       <c r="H298" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="I298" s="14">
-        <v>20</v>
+      <c r="I298" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1" spans="2:9">
@@ -10564,7 +10571,7 @@
         <v>856</v>
       </c>
       <c r="D299" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G299" s="16" t="s">
         <v>503</v>
@@ -10573,7 +10580,7 @@
         <v>504</v>
       </c>
       <c r="I299" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" spans="2:9">
@@ -10583,8 +10590,8 @@
       <c r="C300" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="D300" s="14">
-        <v>20</v>
+      <c r="D300" s="17">
+        <v>32</v>
       </c>
       <c r="G300" s="16" t="s">
         <v>505</v>
@@ -10592,8 +10599,8 @@
       <c r="H300" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="I300" s="14">
-        <v>20</v>
+      <c r="I300" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="301" ht="15" customHeight="1" spans="2:9">
@@ -10604,7 +10611,7 @@
         <v>860</v>
       </c>
       <c r="D301" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G301" s="16" t="s">
         <v>507</v>
@@ -10613,7 +10620,7 @@
         <v>508</v>
       </c>
       <c r="I301" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1" spans="2:9">
@@ -10623,8 +10630,8 @@
       <c r="C302" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="D302" s="14">
-        <v>20</v>
+      <c r="D302" s="17">
+        <v>32</v>
       </c>
       <c r="G302" s="16" t="s">
         <v>509</v>
@@ -10632,8 +10639,8 @@
       <c r="H302" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="I302" s="14">
-        <v>20</v>
+      <c r="I302" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="303" ht="15" customHeight="1" spans="2:9">
@@ -10644,7 +10651,7 @@
         <v>864</v>
       </c>
       <c r="D303" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G303" s="16" t="s">
         <v>511</v>
@@ -10653,7 +10660,7 @@
         <v>512</v>
       </c>
       <c r="I303" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" spans="2:9">
@@ -10663,8 +10670,8 @@
       <c r="C304" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D304" s="14">
-        <v>20</v>
+      <c r="D304" s="17">
+        <v>32</v>
       </c>
       <c r="G304" s="16" t="s">
         <v>513</v>
@@ -10672,8 +10679,8 @@
       <c r="H304" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="I304" s="14">
-        <v>20</v>
+      <c r="I304" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1" spans="2:9">
@@ -10684,7 +10691,7 @@
         <v>868</v>
       </c>
       <c r="D305" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G305" s="18" t="s">
         <v>515</v>
@@ -10693,7 +10700,7 @@
         <v>516</v>
       </c>
       <c r="I305" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" ht="15" customHeight="1" spans="2:9">
@@ -10703,8 +10710,8 @@
       <c r="C306" s="22" t="s">
         <v>870</v>
       </c>
-      <c r="D306" s="23">
-        <v>21</v>
+      <c r="D306" s="17">
+        <v>33</v>
       </c>
       <c r="G306" s="21" t="s">
         <v>517</v>
@@ -10712,8 +10719,8 @@
       <c r="H306" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="I306" s="23">
-        <v>21</v>
+      <c r="I306" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="307" ht="15" customHeight="1" spans="2:9">
@@ -10724,7 +10731,7 @@
         <v>872</v>
       </c>
       <c r="D307" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G307" s="16" t="s">
         <v>519</v>
@@ -10733,7 +10740,7 @@
         <v>520</v>
       </c>
       <c r="I307" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1" spans="2:9">
@@ -10743,8 +10750,8 @@
       <c r="C308" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="D308" s="23">
-        <v>21</v>
+      <c r="D308" s="17">
+        <v>33</v>
       </c>
       <c r="G308" s="16" t="s">
         <v>521</v>
@@ -10752,8 +10759,8 @@
       <c r="H308" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="I308" s="23">
-        <v>21</v>
+      <c r="I308" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1" spans="2:9">
@@ -10764,7 +10771,7 @@
         <v>876</v>
       </c>
       <c r="D309" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G309" s="16" t="s">
         <v>523</v>
@@ -10773,7 +10780,7 @@
         <v>524</v>
       </c>
       <c r="I309" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1" spans="2:9">
@@ -10783,8 +10790,8 @@
       <c r="C310" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="D310" s="23">
-        <v>21</v>
+      <c r="D310" s="17">
+        <v>33</v>
       </c>
       <c r="G310" s="16" t="s">
         <v>525</v>
@@ -10792,8 +10799,8 @@
       <c r="H310" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="I310" s="23">
-        <v>21</v>
+      <c r="I310" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1" spans="2:9">
@@ -10804,7 +10811,7 @@
         <v>880</v>
       </c>
       <c r="D311" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G311" s="16" t="s">
         <v>527</v>
@@ -10813,7 +10820,7 @@
         <v>528</v>
       </c>
       <c r="I311" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="312" ht="15" customHeight="1" spans="2:9">
@@ -10823,8 +10830,8 @@
       <c r="C312" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="D312" s="23">
-        <v>21</v>
+      <c r="D312" s="17">
+        <v>33</v>
       </c>
       <c r="G312" s="16" t="s">
         <v>529</v>
@@ -10832,8 +10839,8 @@
       <c r="H312" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="I312" s="23">
-        <v>21</v>
+      <c r="I312" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" spans="2:9">
@@ -10844,7 +10851,7 @@
         <v>884</v>
       </c>
       <c r="D313" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G313" s="16" t="s">
         <v>531</v>
@@ -10853,7 +10860,7 @@
         <v>532</v>
       </c>
       <c r="I313" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="314" ht="15" customHeight="1" spans="2:9">
@@ -10863,8 +10870,8 @@
       <c r="C314" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="D314" s="23">
-        <v>21</v>
+      <c r="D314" s="17">
+        <v>33</v>
       </c>
       <c r="G314" s="16" t="s">
         <v>533</v>
@@ -10872,8 +10879,8 @@
       <c r="H314" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="I314" s="23">
-        <v>21</v>
+      <c r="I314" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1" spans="2:9">
@@ -10884,7 +10891,7 @@
         <v>888</v>
       </c>
       <c r="D315" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G315" s="16" t="s">
         <v>535</v>
@@ -10893,7 +10900,7 @@
         <v>536</v>
       </c>
       <c r="I315" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1" spans="2:9">
@@ -10903,8 +10910,8 @@
       <c r="C316" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="D316" s="23">
-        <v>21</v>
+      <c r="D316" s="17">
+        <v>33</v>
       </c>
       <c r="G316" s="16" t="s">
         <v>537</v>
@@ -10912,8 +10919,8 @@
       <c r="H316" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="I316" s="23">
-        <v>21</v>
+      <c r="I316" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" spans="2:9">
@@ -10924,7 +10931,7 @@
         <v>892</v>
       </c>
       <c r="D317" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G317" s="16" t="s">
         <v>539</v>
@@ -10933,7 +10940,7 @@
         <v>540</v>
       </c>
       <c r="I317" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1" spans="2:9">
@@ -10943,8 +10950,8 @@
       <c r="C318" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="D318" s="23">
-        <v>21</v>
+      <c r="D318" s="17">
+        <v>33</v>
       </c>
       <c r="G318" s="16" t="s">
         <v>541</v>
@@ -10952,8 +10959,8 @@
       <c r="H318" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="I318" s="23">
-        <v>21</v>
+      <c r="I318" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" spans="2:9">
@@ -10964,7 +10971,7 @@
         <v>896</v>
       </c>
       <c r="D319" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G319" s="16" t="s">
         <v>543</v>
@@ -10973,7 +10980,7 @@
         <v>544</v>
       </c>
       <c r="I319" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1" spans="2:9">
@@ -10983,8 +10990,8 @@
       <c r="C320" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="D320" s="23">
-        <v>21</v>
+      <c r="D320" s="17">
+        <v>33</v>
       </c>
       <c r="G320" s="16" t="s">
         <v>545</v>
@@ -10992,8 +10999,8 @@
       <c r="H320" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="I320" s="23">
-        <v>21</v>
+      <c r="I320" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1" spans="2:9">
@@ -11004,7 +11011,7 @@
         <v>900</v>
       </c>
       <c r="D321" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G321" s="16" t="s">
         <v>547</v>
@@ -11013,7 +11020,7 @@
         <v>548</v>
       </c>
       <c r="I321" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1" spans="2:9">
@@ -11023,8 +11030,8 @@
       <c r="C322" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="D322" s="23">
-        <v>21</v>
+      <c r="D322" s="17">
+        <v>33</v>
       </c>
       <c r="G322" s="16" t="s">
         <v>549</v>
@@ -11032,8 +11039,8 @@
       <c r="H322" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="I322" s="23">
-        <v>21</v>
+      <c r="I322" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1" spans="2:9">
@@ -11044,7 +11051,7 @@
         <v>904</v>
       </c>
       <c r="D323" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G323" s="16" t="s">
         <v>551</v>
@@ -11053,7 +11060,7 @@
         <v>552</v>
       </c>
       <c r="I323" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" ht="15" customHeight="1" spans="2:9">
@@ -11063,8 +11070,8 @@
       <c r="C324" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="D324" s="23">
-        <v>21</v>
+      <c r="D324" s="17">
+        <v>33</v>
       </c>
       <c r="G324" s="16" t="s">
         <v>553</v>
@@ -11072,8 +11079,8 @@
       <c r="H324" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="I324" s="23">
-        <v>21</v>
+      <c r="I324" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1" spans="2:9">
@@ -11084,7 +11091,7 @@
         <v>908</v>
       </c>
       <c r="D325" s="17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G325" s="24" t="s">
         <v>555</v>
@@ -11093,7 +11100,7 @@
         <v>556</v>
       </c>
       <c r="I325" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1" spans="2:9">
@@ -11103,8 +11110,8 @@
       <c r="C326" s="13" t="s">
         <v>910</v>
       </c>
-      <c r="D326" s="14">
-        <v>22</v>
+      <c r="D326" s="17">
+        <v>34</v>
       </c>
       <c r="G326" s="12" t="s">
         <v>557</v>
@@ -11112,8 +11119,8 @@
       <c r="H326" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="I326" s="14">
-        <v>22</v>
+      <c r="I326" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="327" ht="15" customHeight="1" spans="2:9">
@@ -11124,7 +11131,7 @@
         <v>912</v>
       </c>
       <c r="D327" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G327" s="16" t="s">
         <v>560</v>
@@ -11133,7 +11140,7 @@
         <v>561</v>
       </c>
       <c r="I327" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="328" ht="15" customHeight="1" spans="2:9">
@@ -11143,8 +11150,8 @@
       <c r="C328" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="D328" s="14">
-        <v>22</v>
+      <c r="D328" s="17">
+        <v>34</v>
       </c>
       <c r="G328" s="16" t="s">
         <v>563</v>
@@ -11152,8 +11159,8 @@
       <c r="H328" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="I328" s="14">
-        <v>22</v>
+      <c r="I328" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="329" ht="15" customHeight="1" spans="2:9">
@@ -11164,7 +11171,7 @@
         <v>916</v>
       </c>
       <c r="D329" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G329" s="16" t="s">
         <v>566</v>
@@ -11173,7 +11180,7 @@
         <v>567</v>
       </c>
       <c r="I329" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1" spans="2:9">
@@ -11183,8 +11190,8 @@
       <c r="C330" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="D330" s="14">
-        <v>22</v>
+      <c r="D330" s="17">
+        <v>34</v>
       </c>
       <c r="G330" s="16" t="s">
         <v>569</v>
@@ -11192,8 +11199,8 @@
       <c r="H330" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="I330" s="14">
-        <v>22</v>
+      <c r="I330" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="331" ht="15" customHeight="1" spans="2:9">
@@ -11204,7 +11211,7 @@
         <v>920</v>
       </c>
       <c r="D331" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G331" s="16" t="s">
         <v>572</v>
@@ -11213,7 +11220,7 @@
         <v>573</v>
       </c>
       <c r="I331" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="332" ht="15" customHeight="1" spans="2:9">
@@ -11223,8 +11230,8 @@
       <c r="C332" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="D332" s="14">
-        <v>22</v>
+      <c r="D332" s="17">
+        <v>34</v>
       </c>
       <c r="G332" s="16" t="s">
         <v>575</v>
@@ -11232,8 +11239,8 @@
       <c r="H332" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="I332" s="14">
-        <v>22</v>
+      <c r="I332" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" spans="2:9">
@@ -11244,7 +11251,7 @@
         <v>924</v>
       </c>
       <c r="D333" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G333" s="16" t="s">
         <v>578</v>
@@ -11253,7 +11260,7 @@
         <v>579</v>
       </c>
       <c r="I333" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" ht="15" customHeight="1" spans="2:9">
@@ -11263,8 +11270,8 @@
       <c r="C334" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="D334" s="14">
-        <v>22</v>
+      <c r="D334" s="17">
+        <v>34</v>
       </c>
       <c r="G334" s="16" t="s">
         <v>581</v>
@@ -11272,8 +11279,8 @@
       <c r="H334" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="I334" s="14">
-        <v>22</v>
+      <c r="I334" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1" spans="2:9">
@@ -11284,7 +11291,7 @@
         <v>928</v>
       </c>
       <c r="D335" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G335" s="16" t="s">
         <v>584</v>
@@ -11293,7 +11300,7 @@
         <v>585</v>
       </c>
       <c r="I335" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="336" ht="15" customHeight="1" spans="2:9">
@@ -11303,8 +11310,8 @@
       <c r="C336" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="D336" s="14">
-        <v>22</v>
+      <c r="D336" s="17">
+        <v>34</v>
       </c>
       <c r="G336" s="16" t="s">
         <v>587</v>
@@ -11312,8 +11319,8 @@
       <c r="H336" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="I336" s="14">
-        <v>22</v>
+      <c r="I336" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="337" ht="15" customHeight="1" spans="2:9">
@@ -11324,7 +11331,7 @@
         <v>932</v>
       </c>
       <c r="D337" s="17">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G337" s="18" t="s">
         <v>590</v>
@@ -11333,7 +11340,7 @@
         <v>591</v>
       </c>
       <c r="I337" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338" ht="15" customHeight="1" spans="2:9">
@@ -11343,8 +11350,8 @@
       <c r="C338" s="22" t="s">
         <v>934</v>
       </c>
-      <c r="D338" s="23">
-        <v>23</v>
+      <c r="D338" s="17">
+        <v>35</v>
       </c>
       <c r="G338" s="21" t="s">
         <v>593</v>
@@ -11352,8 +11359,8 @@
       <c r="H338" s="22" t="s">
         <v>594</v>
       </c>
-      <c r="I338" s="23">
-        <v>23</v>
+      <c r="I338" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="339" ht="15" customHeight="1" spans="2:9">
@@ -11364,7 +11371,7 @@
         <v>936</v>
       </c>
       <c r="D339" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G339" s="16" t="s">
         <v>596</v>
@@ -11373,7 +11380,7 @@
         <v>597</v>
       </c>
       <c r="I339" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1" spans="2:9">
@@ -11383,8 +11390,8 @@
       <c r="C340" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="D340" s="23">
-        <v>23</v>
+      <c r="D340" s="17">
+        <v>35</v>
       </c>
       <c r="G340" s="16" t="s">
         <v>599</v>
@@ -11392,8 +11399,8 @@
       <c r="H340" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="I340" s="23">
-        <v>23</v>
+      <c r="I340" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="341" ht="15" customHeight="1" spans="2:9">
@@ -11404,7 +11411,7 @@
         <v>940</v>
       </c>
       <c r="D341" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G341" s="16" t="s">
         <v>602</v>
@@ -11413,7 +11420,7 @@
         <v>603</v>
       </c>
       <c r="I341" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="342" ht="15" customHeight="1" spans="2:9">
@@ -11423,8 +11430,8 @@
       <c r="C342" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="D342" s="23">
-        <v>23</v>
+      <c r="D342" s="17">
+        <v>35</v>
       </c>
       <c r="G342" s="16" t="s">
         <v>605</v>
@@ -11432,8 +11439,8 @@
       <c r="H342" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="I342" s="23">
-        <v>23</v>
+      <c r="I342" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="343" ht="15" customHeight="1" spans="2:9">
@@ -11444,7 +11451,7 @@
         <v>944</v>
       </c>
       <c r="D343" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G343" s="16" t="s">
         <v>608</v>
@@ -11453,7 +11460,7 @@
         <v>609</v>
       </c>
       <c r="I343" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="344" ht="15" customHeight="1" spans="2:9">
@@ -11463,8 +11470,8 @@
       <c r="C344" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="D344" s="23">
-        <v>23</v>
+      <c r="D344" s="17">
+        <v>35</v>
       </c>
       <c r="G344" s="16" t="s">
         <v>611</v>
@@ -11472,8 +11479,8 @@
       <c r="H344" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="I344" s="23">
-        <v>23</v>
+      <c r="I344" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1" spans="2:9">
@@ -11484,7 +11491,7 @@
         <v>948</v>
       </c>
       <c r="D345" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G345" s="16" t="s">
         <v>614</v>
@@ -11493,7 +11500,7 @@
         <v>615</v>
       </c>
       <c r="I345" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="346" ht="15" customHeight="1" spans="2:9">
@@ -11503,8 +11510,8 @@
       <c r="C346" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="D346" s="23">
-        <v>23</v>
+      <c r="D346" s="17">
+        <v>35</v>
       </c>
       <c r="G346" s="16" t="s">
         <v>617</v>
@@ -11512,8 +11519,8 @@
       <c r="H346" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="I346" s="23">
-        <v>23</v>
+      <c r="I346" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="347" ht="15" customHeight="1" spans="2:9">
@@ -11524,7 +11531,7 @@
         <v>952</v>
       </c>
       <c r="D347" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G347" s="16" t="s">
         <v>620</v>
@@ -11533,7 +11540,7 @@
         <v>621</v>
       </c>
       <c r="I347" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="348" ht="15" customHeight="1" spans="2:9">
@@ -11543,8 +11550,8 @@
       <c r="C348" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="D348" s="23">
-        <v>23</v>
+      <c r="D348" s="17">
+        <v>35</v>
       </c>
       <c r="G348" s="16" t="s">
         <v>623</v>
@@ -11552,8 +11559,8 @@
       <c r="H348" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="I348" s="23">
-        <v>23</v>
+      <c r="I348" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="349" ht="15" customHeight="1" spans="2:9">
@@ -11564,7 +11571,7 @@
         <v>956</v>
       </c>
       <c r="D349" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G349" s="16" t="s">
         <v>626</v>
@@ -11573,7 +11580,7 @@
         <v>627</v>
       </c>
       <c r="I349" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1" spans="2:9">
@@ -11583,8 +11590,8 @@
       <c r="C350" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="D350" s="23">
-        <v>23</v>
+      <c r="D350" s="17">
+        <v>35</v>
       </c>
       <c r="G350" s="16" t="s">
         <v>629</v>
@@ -11592,8 +11599,8 @@
       <c r="H350" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="I350" s="23">
-        <v>23</v>
+      <c r="I350" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="351" ht="15" customHeight="1" spans="2:9">
@@ -11604,7 +11611,7 @@
         <v>960</v>
       </c>
       <c r="D351" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G351" s="16" t="s">
         <v>632</v>
@@ -11613,7 +11620,7 @@
         <v>633</v>
       </c>
       <c r="I351" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" ht="15" customHeight="1" spans="2:9">
@@ -11623,8 +11630,8 @@
       <c r="C352" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="D352" s="23">
-        <v>23</v>
+      <c r="D352" s="17">
+        <v>35</v>
       </c>
       <c r="G352" s="16" t="s">
         <v>635</v>
@@ -11632,8 +11639,8 @@
       <c r="H352" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="I352" s="23">
-        <v>23</v>
+      <c r="I352" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="353" ht="15" customHeight="1" spans="2:9">
@@ -11644,7 +11651,7 @@
         <v>964</v>
       </c>
       <c r="D353" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G353" s="16" t="s">
         <v>638</v>
@@ -11653,7 +11660,7 @@
         <v>639</v>
       </c>
       <c r="I353" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354" ht="15" customHeight="1" spans="2:9">
@@ -11663,8 +11670,8 @@
       <c r="C354" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="D354" s="23">
-        <v>23</v>
+      <c r="D354" s="17">
+        <v>35</v>
       </c>
       <c r="G354" s="16" t="s">
         <v>641</v>
@@ -11672,8 +11679,8 @@
       <c r="H354" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="I354" s="23">
-        <v>23</v>
+      <c r="I354" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1" spans="2:9">
@@ -11684,7 +11691,7 @@
         <v>968</v>
       </c>
       <c r="D355" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G355" s="16" t="s">
         <v>644</v>
@@ -11693,7 +11700,7 @@
         <v>645</v>
       </c>
       <c r="I355" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="356" ht="15" customHeight="1" spans="2:9">
@@ -11703,8 +11710,8 @@
       <c r="C356" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="D356" s="23">
-        <v>23</v>
+      <c r="D356" s="17">
+        <v>35</v>
       </c>
       <c r="G356" s="16" t="s">
         <v>647</v>
@@ -11712,8 +11719,8 @@
       <c r="H356" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="I356" s="23">
-        <v>23</v>
+      <c r="I356" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="357" ht="15" customHeight="1" spans="2:9">
@@ -11724,7 +11731,7 @@
         <v>972</v>
       </c>
       <c r="D357" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G357" s="24" t="s">
         <v>650</v>
@@ -11733,7 +11740,7 @@
         <v>651</v>
       </c>
       <c r="I357" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="358" ht="15" customHeight="1" spans="2:9">
@@ -11743,8 +11750,8 @@
       <c r="C358" s="13" t="s">
         <v>974</v>
       </c>
-      <c r="D358" s="14">
-        <v>24</v>
+      <c r="D358" s="17">
+        <v>36</v>
       </c>
       <c r="G358" s="12" t="s">
         <v>973</v>
@@ -11752,8 +11759,8 @@
       <c r="H358" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="I358" s="14">
-        <v>24</v>
+      <c r="I358" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="359" ht="15" customHeight="1" spans="2:9">
@@ -11764,7 +11771,7 @@
         <v>976</v>
       </c>
       <c r="D359" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G359" s="16" t="s">
         <v>975</v>
@@ -11773,7 +11780,7 @@
         <v>657</v>
       </c>
       <c r="I359" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1" spans="2:9">
@@ -11783,8 +11790,8 @@
       <c r="C360" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="D360" s="14">
-        <v>24</v>
+      <c r="D360" s="17">
+        <v>36</v>
       </c>
       <c r="G360" s="16" t="s">
         <v>977</v>
@@ -11792,8 +11799,8 @@
       <c r="H360" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="I360" s="14">
-        <v>24</v>
+      <c r="I360" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="361" ht="15" customHeight="1" spans="2:9">
@@ -11804,7 +11811,7 @@
         <v>980</v>
       </c>
       <c r="D361" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G361" s="16" t="s">
         <v>979</v>
@@ -11813,7 +11820,7 @@
         <v>663</v>
       </c>
       <c r="I361" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="362" ht="15" customHeight="1" spans="2:9">
@@ -11823,8 +11830,8 @@
       <c r="C362" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="D362" s="14">
-        <v>24</v>
+      <c r="D362" s="17">
+        <v>36</v>
       </c>
       <c r="G362" s="16" t="s">
         <v>981</v>
@@ -11832,8 +11839,8 @@
       <c r="H362" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="I362" s="14">
-        <v>24</v>
+      <c r="I362" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1" spans="2:9">
@@ -11844,7 +11851,7 @@
         <v>984</v>
       </c>
       <c r="D363" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G363" s="16" t="s">
         <v>983</v>
@@ -11853,7 +11860,7 @@
         <v>669</v>
       </c>
       <c r="I363" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="364" ht="15" customHeight="1" spans="2:9">
@@ -11863,8 +11870,8 @@
       <c r="C364" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="D364" s="14">
-        <v>24</v>
+      <c r="D364" s="17">
+        <v>36</v>
       </c>
       <c r="G364" s="16" t="s">
         <v>985</v>
@@ -11872,8 +11879,8 @@
       <c r="H364" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="I364" s="14">
-        <v>24</v>
+      <c r="I364" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1" spans="2:9">
@@ -11884,7 +11891,7 @@
         <v>988</v>
       </c>
       <c r="D365" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G365" s="16" t="s">
         <v>987</v>
@@ -11893,7 +11900,7 @@
         <v>675</v>
       </c>
       <c r="I365" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1" spans="2:9">
@@ -11903,8 +11910,8 @@
       <c r="C366" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D366" s="14">
-        <v>24</v>
+      <c r="D366" s="17">
+        <v>36</v>
       </c>
       <c r="G366" s="16" t="s">
         <v>989</v>
@@ -11912,8 +11919,8 @@
       <c r="H366" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="I366" s="14">
-        <v>24</v>
+      <c r="I366" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="367" ht="15" customHeight="1" spans="2:9">
@@ -11924,7 +11931,7 @@
         <v>992</v>
       </c>
       <c r="D367" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G367" s="16" t="s">
         <v>991</v>
@@ -11933,7 +11940,7 @@
         <v>681</v>
       </c>
       <c r="I367" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="368" ht="15" customHeight="1" spans="2:9">
@@ -11943,8 +11950,8 @@
       <c r="C368" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="D368" s="14">
-        <v>24</v>
+      <c r="D368" s="17">
+        <v>36</v>
       </c>
       <c r="G368" s="16" t="s">
         <v>993</v>
@@ -11952,8 +11959,8 @@
       <c r="H368" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="I368" s="14">
-        <v>24</v>
+      <c r="I368" s="17">
+        <v>37</v>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1" spans="2:9">
@@ -11964,7 +11971,7 @@
         <v>996</v>
       </c>
       <c r="D369" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G369" s="18" t="s">
         <v>995</v>
@@ -11973,7 +11980,7 @@
         <v>687</v>
       </c>
       <c r="I369" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1" spans="2:9">
@@ -11983,8 +11990,8 @@
       <c r="C370" s="22" t="s">
         <v>998</v>
       </c>
-      <c r="D370" s="23">
-        <v>25</v>
+      <c r="D370" s="17">
+        <v>38</v>
       </c>
       <c r="G370" s="21" t="s">
         <v>689</v>
@@ -11992,8 +11999,8 @@
       <c r="H370" s="22" t="s">
         <v>998</v>
       </c>
-      <c r="I370" s="23">
-        <v>25</v>
+      <c r="I370" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="371" ht="15" customHeight="1" spans="2:9">
@@ -12004,7 +12011,7 @@
         <v>1000</v>
       </c>
       <c r="D371" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G371" s="16" t="s">
         <v>692</v>
@@ -12013,7 +12020,7 @@
         <v>1000</v>
       </c>
       <c r="I371" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="372" ht="15" customHeight="1" spans="2:9">
@@ -12023,8 +12030,8 @@
       <c r="C372" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D372" s="23">
-        <v>25</v>
+      <c r="D372" s="17">
+        <v>38</v>
       </c>
       <c r="G372" s="16" t="s">
         <v>695</v>
@@ -12032,8 +12039,8 @@
       <c r="H372" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="I372" s="23">
-        <v>25</v>
+      <c r="I372" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="373" ht="15" customHeight="1" spans="2:9">
@@ -12044,7 +12051,7 @@
         <v>1004</v>
       </c>
       <c r="D373" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G373" s="16" t="s">
         <v>698</v>
@@ -12053,7 +12060,7 @@
         <v>1004</v>
       </c>
       <c r="I373" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="374" ht="15" customHeight="1" spans="2:9">
@@ -12063,8 +12070,8 @@
       <c r="C374" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="D374" s="23">
-        <v>25</v>
+      <c r="D374" s="17">
+        <v>38</v>
       </c>
       <c r="G374" s="16" t="s">
         <v>701</v>
@@ -12072,8 +12079,8 @@
       <c r="H374" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="I374" s="23">
-        <v>25</v>
+      <c r="I374" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1" spans="2:9">
@@ -12084,7 +12091,7 @@
         <v>1008</v>
       </c>
       <c r="D375" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G375" s="16" t="s">
         <v>704</v>
@@ -12093,7 +12100,7 @@
         <v>1008</v>
       </c>
       <c r="I375" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="376" ht="15" customHeight="1" spans="2:9">
@@ -12103,8 +12110,8 @@
       <c r="C376" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="D376" s="23">
-        <v>25</v>
+      <c r="D376" s="17">
+        <v>38</v>
       </c>
       <c r="G376" s="16" t="s">
         <v>707</v>
@@ -12112,8 +12119,8 @@
       <c r="H376" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="I376" s="23">
-        <v>25</v>
+      <c r="I376" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="377" ht="15" customHeight="1" spans="2:9">
@@ -12124,7 +12131,7 @@
         <v>1012</v>
       </c>
       <c r="D377" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G377" s="16" t="s">
         <v>710</v>
@@ -12133,7 +12140,7 @@
         <v>1012</v>
       </c>
       <c r="I377" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="378" ht="15" customHeight="1" spans="2:9">
@@ -12143,8 +12150,8 @@
       <c r="C378" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="D378" s="23">
-        <v>25</v>
+      <c r="D378" s="17">
+        <v>38</v>
       </c>
       <c r="G378" s="16" t="s">
         <v>713</v>
@@ -12152,8 +12159,8 @@
       <c r="H378" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="I378" s="23">
-        <v>25</v>
+      <c r="I378" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="379" ht="15" customHeight="1" spans="2:9">
@@ -12164,7 +12171,7 @@
         <v>1016</v>
       </c>
       <c r="D379" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G379" s="16" t="s">
         <v>716</v>
@@ -12173,7 +12180,7 @@
         <v>1016</v>
       </c>
       <c r="I379" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1" spans="2:9">
@@ -12183,8 +12190,8 @@
       <c r="C380" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="D380" s="23">
-        <v>25</v>
+      <c r="D380" s="17">
+        <v>38</v>
       </c>
       <c r="G380" s="16" t="s">
         <v>719</v>
@@ -12192,8 +12199,8 @@
       <c r="H380" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="I380" s="23">
-        <v>25</v>
+      <c r="I380" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="381" ht="15" customHeight="1" spans="2:9">
@@ -12204,7 +12211,7 @@
         <v>1020</v>
       </c>
       <c r="D381" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G381" s="16" t="s">
         <v>722</v>
@@ -12213,7 +12220,7 @@
         <v>1020</v>
       </c>
       <c r="I381" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="382" ht="15" customHeight="1" spans="2:9">
@@ -12223,8 +12230,8 @@
       <c r="C382" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="D382" s="23">
-        <v>25</v>
+      <c r="D382" s="17">
+        <v>38</v>
       </c>
       <c r="G382" s="16" t="s">
         <v>725</v>
@@ -12232,8 +12239,8 @@
       <c r="H382" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="I382" s="23">
-        <v>25</v>
+      <c r="I382" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="383" ht="15" customHeight="1" spans="2:9">
@@ -12244,7 +12251,7 @@
         <v>1024</v>
       </c>
       <c r="D383" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G383" s="16" t="s">
         <v>728</v>
@@ -12253,7 +12260,7 @@
         <v>1024</v>
       </c>
       <c r="I383" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="384" ht="15" customHeight="1" spans="2:9">
@@ -12263,8 +12270,8 @@
       <c r="C384" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="D384" s="23">
-        <v>25</v>
+      <c r="D384" s="17">
+        <v>38</v>
       </c>
       <c r="G384" s="16" t="s">
         <v>731</v>
@@ -12272,8 +12279,8 @@
       <c r="H384" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="I384" s="23">
-        <v>25</v>
+      <c r="I384" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1" spans="2:9">
@@ -12284,7 +12291,7 @@
         <v>1028</v>
       </c>
       <c r="D385" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G385" s="16" t="s">
         <v>734</v>
@@ -12293,7 +12300,7 @@
         <v>1028</v>
       </c>
       <c r="I385" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="386" ht="15" customHeight="1" spans="2:9">
@@ -12303,8 +12310,8 @@
       <c r="C386" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="D386" s="23">
-        <v>25</v>
+      <c r="D386" s="17">
+        <v>38</v>
       </c>
       <c r="G386" s="16" t="s">
         <v>737</v>
@@ -12312,8 +12319,8 @@
       <c r="H386" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="I386" s="23">
-        <v>25</v>
+      <c r="I386" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="387" ht="15" customHeight="1" spans="2:9">
@@ -12324,7 +12331,7 @@
         <v>1032</v>
       </c>
       <c r="D387" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G387" s="16" t="s">
         <v>740</v>
@@ -12333,7 +12340,7 @@
         <v>1032</v>
       </c>
       <c r="I387" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="388" ht="15" customHeight="1" spans="2:9">
@@ -12343,8 +12350,8 @@
       <c r="C388" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="D388" s="23">
-        <v>25</v>
+      <c r="D388" s="17">
+        <v>38</v>
       </c>
       <c r="G388" s="16" t="s">
         <v>743</v>
@@ -12352,8 +12359,8 @@
       <c r="H388" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="I388" s="23">
-        <v>25</v>
+      <c r="I388" s="17">
+        <v>39</v>
       </c>
     </row>
     <row r="389" ht="15" customHeight="1" spans="2:9">
@@ -12364,7 +12371,7 @@
         <v>1036</v>
       </c>
       <c r="D389" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G389" s="24" t="s">
         <v>746</v>
@@ -12373,7 +12380,7 @@
         <v>1036</v>
       </c>
       <c r="I389" s="17">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1" spans="2:9">
@@ -12383,8 +12390,8 @@
       <c r="C390" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="D390" s="14">
-        <v>26</v>
+      <c r="D390" s="17">
+        <v>40</v>
       </c>
       <c r="G390" s="15" t="s">
         <v>909</v>
@@ -12392,8 +12399,8 @@
       <c r="H390" s="13" t="s">
         <v>910</v>
       </c>
-      <c r="I390" s="14">
-        <v>26</v>
+      <c r="I390" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1" spans="2:9">
@@ -12404,7 +12411,7 @@
         <v>754</v>
       </c>
       <c r="D391" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G391" s="16" t="s">
         <v>911</v>
@@ -12413,7 +12420,7 @@
         <v>912</v>
       </c>
       <c r="I391" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="392" ht="15" customHeight="1" spans="2:9">
@@ -12423,8 +12430,8 @@
       <c r="C392" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="D392" s="14">
-        <v>26</v>
+      <c r="D392" s="17">
+        <v>40</v>
       </c>
       <c r="G392" s="16" t="s">
         <v>913</v>
@@ -12432,8 +12439,8 @@
       <c r="H392" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="I392" s="14">
-        <v>26</v>
+      <c r="I392" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="393" ht="15" customHeight="1" spans="2:9">
@@ -12444,7 +12451,7 @@
         <v>760</v>
       </c>
       <c r="D393" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G393" s="16" t="s">
         <v>915</v>
@@ -12453,7 +12460,7 @@
         <v>916</v>
       </c>
       <c r="I393" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="394" ht="15" customHeight="1" spans="2:9">
@@ -12463,8 +12470,8 @@
       <c r="C394" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="D394" s="14">
-        <v>26</v>
+      <c r="D394" s="17">
+        <v>40</v>
       </c>
       <c r="G394" s="16" t="s">
         <v>917</v>
@@ -12472,8 +12479,8 @@
       <c r="H394" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="I394" s="14">
-        <v>26</v>
+      <c r="I394" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1" spans="2:9">
@@ -12484,7 +12491,7 @@
         <v>766</v>
       </c>
       <c r="D395" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G395" s="16" t="s">
         <v>919</v>
@@ -12493,7 +12500,7 @@
         <v>920</v>
       </c>
       <c r="I395" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="396" ht="15" customHeight="1" spans="2:9">
@@ -12503,8 +12510,8 @@
       <c r="C396" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="D396" s="14">
-        <v>26</v>
+      <c r="D396" s="17">
+        <v>40</v>
       </c>
       <c r="G396" s="16" t="s">
         <v>921</v>
@@ -12512,8 +12519,8 @@
       <c r="H396" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="I396" s="14">
-        <v>26</v>
+      <c r="I396" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="397" ht="15" customHeight="1" spans="2:9">
@@ -12524,7 +12531,7 @@
         <v>772</v>
       </c>
       <c r="D397" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G397" s="16" t="s">
         <v>923</v>
@@ -12533,7 +12540,7 @@
         <v>924</v>
       </c>
       <c r="I397" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="398" ht="15" customHeight="1" spans="2:9">
@@ -12543,8 +12550,8 @@
       <c r="C398" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="D398" s="14">
-        <v>26</v>
+      <c r="D398" s="17">
+        <v>40</v>
       </c>
       <c r="G398" s="16" t="s">
         <v>925</v>
@@ -12552,8 +12559,8 @@
       <c r="H398" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="I398" s="14">
-        <v>26</v>
+      <c r="I398" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="399" ht="15" customHeight="1" spans="2:9">
@@ -12564,7 +12571,7 @@
         <v>778</v>
       </c>
       <c r="D399" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G399" s="16" t="s">
         <v>927</v>
@@ -12573,7 +12580,7 @@
         <v>928</v>
       </c>
       <c r="I399" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1" spans="2:9">
@@ -12583,8 +12590,8 @@
       <c r="C400" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="D400" s="14">
-        <v>26</v>
+      <c r="D400" s="17">
+        <v>40</v>
       </c>
       <c r="G400" s="16" t="s">
         <v>929</v>
@@ -12592,8 +12599,8 @@
       <c r="H400" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="I400" s="14">
-        <v>26</v>
+      <c r="I400" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="401" ht="15" customHeight="1" spans="2:9">
@@ -12604,7 +12611,7 @@
         <v>784</v>
       </c>
       <c r="D401" s="17">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G401" s="18" t="s">
         <v>931</v>
@@ -12613,7 +12620,7 @@
         <v>932</v>
       </c>
       <c r="I401" s="17">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="402" ht="15" customHeight="1" spans="2:9">
@@ -12623,8 +12630,8 @@
       <c r="C402" s="22" t="s">
         <v>595</v>
       </c>
-      <c r="D402" s="23">
-        <v>27</v>
+      <c r="D402" s="17">
+        <v>41</v>
       </c>
       <c r="G402" s="21" t="s">
         <v>933</v>
@@ -12632,8 +12639,8 @@
       <c r="H402" s="22" t="s">
         <v>934</v>
       </c>
-      <c r="I402" s="23">
-        <v>27</v>
+      <c r="I402" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="403" ht="15" customHeight="1" spans="2:9">
@@ -12644,7 +12651,7 @@
         <v>598</v>
       </c>
       <c r="D403" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G403" s="16" t="s">
         <v>935</v>
@@ -12653,7 +12660,7 @@
         <v>936</v>
       </c>
       <c r="I403" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="404" ht="15" customHeight="1" spans="2:9">
@@ -12663,8 +12670,8 @@
       <c r="C404" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D404" s="23">
-        <v>27</v>
+      <c r="D404" s="17">
+        <v>41</v>
       </c>
       <c r="G404" s="16" t="s">
         <v>937</v>
@@ -12672,8 +12679,8 @@
       <c r="H404" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="I404" s="23">
-        <v>27</v>
+      <c r="I404" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1" spans="2:9">
@@ -12684,7 +12691,7 @@
         <v>604</v>
       </c>
       <c r="D405" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G405" s="16" t="s">
         <v>939</v>
@@ -12693,7 +12700,7 @@
         <v>940</v>
       </c>
       <c r="I405" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="406" ht="15" customHeight="1" spans="2:9">
@@ -12703,8 +12710,8 @@
       <c r="C406" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D406" s="23">
-        <v>27</v>
+      <c r="D406" s="17">
+        <v>41</v>
       </c>
       <c r="G406" s="16" t="s">
         <v>941</v>
@@ -12712,8 +12719,8 @@
       <c r="H406" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="I406" s="23">
-        <v>27</v>
+      <c r="I406" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="407" ht="15" customHeight="1" spans="2:9">
@@ -12724,7 +12731,7 @@
         <v>610</v>
       </c>
       <c r="D407" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G407" s="16" t="s">
         <v>943</v>
@@ -12733,7 +12740,7 @@
         <v>944</v>
       </c>
       <c r="I407" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="408" ht="15" customHeight="1" spans="2:9">
@@ -12743,8 +12750,8 @@
       <c r="C408" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="D408" s="23">
-        <v>27</v>
+      <c r="D408" s="17">
+        <v>41</v>
       </c>
       <c r="G408" s="16" t="s">
         <v>945</v>
@@ -12752,8 +12759,8 @@
       <c r="H408" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="I408" s="23">
-        <v>27</v>
+      <c r="I408" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="409" ht="15" customHeight="1" spans="2:9">
@@ -12764,7 +12771,7 @@
         <v>616</v>
       </c>
       <c r="D409" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G409" s="16" t="s">
         <v>947</v>
@@ -12773,7 +12780,7 @@
         <v>948</v>
       </c>
       <c r="I409" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1" spans="2:9">
@@ -12783,8 +12790,8 @@
       <c r="C410" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="D410" s="23">
-        <v>27</v>
+      <c r="D410" s="17">
+        <v>41</v>
       </c>
       <c r="G410" s="16" t="s">
         <v>949</v>
@@ -12792,8 +12799,8 @@
       <c r="H410" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="I410" s="23">
-        <v>27</v>
+      <c r="I410" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="411" ht="15" customHeight="1" spans="2:9">
@@ -12804,7 +12811,7 @@
         <v>622</v>
       </c>
       <c r="D411" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G411" s="16" t="s">
         <v>951</v>
@@ -12813,7 +12820,7 @@
         <v>952</v>
       </c>
       <c r="I411" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="412" ht="15" customHeight="1" spans="2:9">
@@ -12823,8 +12830,8 @@
       <c r="C412" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D412" s="23">
-        <v>27</v>
+      <c r="D412" s="17">
+        <v>41</v>
       </c>
       <c r="G412" s="16" t="s">
         <v>953</v>
@@ -12832,8 +12839,8 @@
       <c r="H412" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="I412" s="23">
-        <v>27</v>
+      <c r="I412" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="413" ht="15" customHeight="1" spans="2:9">
@@ -12844,7 +12851,7 @@
         <v>628</v>
       </c>
       <c r="D413" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G413" s="16" t="s">
         <v>955</v>
@@ -12853,7 +12860,7 @@
         <v>956</v>
       </c>
       <c r="I413" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="414" ht="15" customHeight="1" spans="2:9">
@@ -12863,8 +12870,8 @@
       <c r="C414" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D414" s="23">
-        <v>27</v>
+      <c r="D414" s="17">
+        <v>41</v>
       </c>
       <c r="G414" s="16" t="s">
         <v>957</v>
@@ -12872,8 +12879,8 @@
       <c r="H414" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="I414" s="23">
-        <v>27</v>
+      <c r="I414" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1" spans="2:9">
@@ -12884,7 +12891,7 @@
         <v>634</v>
       </c>
       <c r="D415" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G415" s="16" t="s">
         <v>959</v>
@@ -12893,7 +12900,7 @@
         <v>960</v>
       </c>
       <c r="I415" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="416" ht="15" customHeight="1" spans="2:9">
@@ -12903,8 +12910,8 @@
       <c r="C416" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D416" s="23">
-        <v>27</v>
+      <c r="D416" s="17">
+        <v>41</v>
       </c>
       <c r="G416" s="16" t="s">
         <v>961</v>
@@ -12912,8 +12919,8 @@
       <c r="H416" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="I416" s="23">
-        <v>27</v>
+      <c r="I416" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="417" ht="15" customHeight="1" spans="2:9">
@@ -12924,7 +12931,7 @@
         <v>640</v>
       </c>
       <c r="D417" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G417" s="16" t="s">
         <v>963</v>
@@ -12933,7 +12940,7 @@
         <v>964</v>
       </c>
       <c r="I417" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="418" ht="15" customHeight="1" spans="2:9">
@@ -12943,8 +12950,8 @@
       <c r="C418" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="D418" s="23">
-        <v>27</v>
+      <c r="D418" s="17">
+        <v>41</v>
       </c>
       <c r="G418" s="16" t="s">
         <v>965</v>
@@ -12952,8 +12959,8 @@
       <c r="H418" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="I418" s="23">
-        <v>27</v>
+      <c r="I418" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="419" ht="15" customHeight="1" spans="2:9">
@@ -12964,7 +12971,7 @@
         <v>646</v>
       </c>
       <c r="D419" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G419" s="16" t="s">
         <v>967</v>
@@ -12973,7 +12980,7 @@
         <v>968</v>
       </c>
       <c r="I419" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1" spans="2:9">
@@ -12983,8 +12990,8 @@
       <c r="C420" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D420" s="23">
-        <v>27</v>
+      <c r="D420" s="17">
+        <v>41</v>
       </c>
       <c r="G420" s="16" t="s">
         <v>969</v>
@@ -12992,8 +12999,8 @@
       <c r="H420" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="I420" s="23">
-        <v>27</v>
+      <c r="I420" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="421" ht="15" customHeight="1" spans="2:9">
@@ -13004,7 +13011,7 @@
         <v>652</v>
       </c>
       <c r="D421" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G421" s="24" t="s">
         <v>971</v>
@@ -13013,7 +13020,7 @@
         <v>972</v>
       </c>
       <c r="I421" s="17">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="422" ht="15" customHeight="1" spans="2:9">
@@ -13023,8 +13030,8 @@
       <c r="C422" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="D422" s="14">
-        <v>28</v>
+      <c r="D422" s="17">
+        <v>42</v>
       </c>
       <c r="G422" s="12" t="s">
         <v>653</v>
@@ -13032,8 +13039,8 @@
       <c r="H422" s="13" t="s">
         <v>974</v>
       </c>
-      <c r="I422" s="14">
-        <v>28</v>
+      <c r="I422" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="423" ht="15" customHeight="1" spans="2:9">
@@ -13044,7 +13051,7 @@
         <v>658</v>
       </c>
       <c r="D423" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G423" s="16" t="s">
         <v>656</v>
@@ -13053,7 +13060,7 @@
         <v>976</v>
       </c>
       <c r="I423" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="424" ht="15" customHeight="1" spans="2:9">
@@ -13063,8 +13070,8 @@
       <c r="C424" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="D424" s="14">
-        <v>28</v>
+      <c r="D424" s="17">
+        <v>42</v>
       </c>
       <c r="G424" s="16" t="s">
         <v>659</v>
@@ -13072,8 +13079,8 @@
       <c r="H424" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="I424" s="14">
-        <v>28</v>
+      <c r="I424" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1" spans="2:9">
@@ -13084,7 +13091,7 @@
         <v>664</v>
       </c>
       <c r="D425" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G425" s="16" t="s">
         <v>662</v>
@@ -13093,7 +13100,7 @@
         <v>980</v>
       </c>
       <c r="I425" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="426" ht="15" customHeight="1" spans="2:9">
@@ -13103,8 +13110,8 @@
       <c r="C426" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="D426" s="14">
-        <v>28</v>
+      <c r="D426" s="17">
+        <v>42</v>
       </c>
       <c r="G426" s="16" t="s">
         <v>665</v>
@@ -13112,8 +13119,8 @@
       <c r="H426" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="I426" s="14">
-        <v>28</v>
+      <c r="I426" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="427" ht="15" customHeight="1" spans="2:9">
@@ -13124,7 +13131,7 @@
         <v>670</v>
       </c>
       <c r="D427" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G427" s="16" t="s">
         <v>668</v>
@@ -13133,7 +13140,7 @@
         <v>984</v>
       </c>
       <c r="I427" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="428" ht="15" customHeight="1" spans="2:9">
@@ -13143,8 +13150,8 @@
       <c r="C428" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="D428" s="14">
-        <v>28</v>
+      <c r="D428" s="17">
+        <v>42</v>
       </c>
       <c r="G428" s="16" t="s">
         <v>671</v>
@@ -13152,8 +13159,8 @@
       <c r="H428" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="I428" s="14">
-        <v>28</v>
+      <c r="I428" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="429" ht="15" customHeight="1" spans="2:9">
@@ -13164,7 +13171,7 @@
         <v>676</v>
       </c>
       <c r="D429" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G429" s="16" t="s">
         <v>674</v>
@@ -13173,7 +13180,7 @@
         <v>988</v>
       </c>
       <c r="I429" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1" spans="2:9">
@@ -13183,8 +13190,8 @@
       <c r="C430" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D430" s="14">
-        <v>28</v>
+      <c r="D430" s="17">
+        <v>42</v>
       </c>
       <c r="G430" s="16" t="s">
         <v>677</v>
@@ -13192,8 +13199,8 @@
       <c r="H430" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="I430" s="14">
-        <v>28</v>
+      <c r="I430" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="431" ht="15" customHeight="1" spans="2:9">
@@ -13204,7 +13211,7 @@
         <v>682</v>
       </c>
       <c r="D431" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G431" s="16" t="s">
         <v>680</v>
@@ -13213,7 +13220,7 @@
         <v>992</v>
       </c>
       <c r="I431" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="432" ht="15" customHeight="1" spans="2:9">
@@ -13223,8 +13230,8 @@
       <c r="C432" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="D432" s="14">
-        <v>28</v>
+      <c r="D432" s="17">
+        <v>42</v>
       </c>
       <c r="G432" s="16" t="s">
         <v>683</v>
@@ -13232,8 +13239,8 @@
       <c r="H432" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="I432" s="14">
-        <v>28</v>
+      <c r="I432" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="433" ht="15" customHeight="1" spans="2:9">
@@ -13244,7 +13251,7 @@
         <v>688</v>
       </c>
       <c r="D433" s="17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G433" s="18" t="s">
         <v>686</v>
@@ -13253,7 +13260,7 @@
         <v>996</v>
       </c>
       <c r="I433" s="17">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="434" ht="15" customHeight="1" spans="2:9">
@@ -13263,8 +13270,8 @@
       <c r="C434" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D434" s="23">
-        <v>29</v>
+      <c r="D434" s="17">
+        <v>44</v>
       </c>
       <c r="G434" s="21" t="s">
         <v>997</v>
@@ -13272,8 +13279,8 @@
       <c r="H434" s="22" t="s">
         <v>690</v>
       </c>
-      <c r="I434" s="23">
-        <v>29</v>
+      <c r="I434" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1" spans="2:9">
@@ -13284,7 +13291,7 @@
         <v>118</v>
       </c>
       <c r="D435" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G435" s="16" t="s">
         <v>999</v>
@@ -13293,7 +13300,7 @@
         <v>693</v>
       </c>
       <c r="I435" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="436" ht="15" customHeight="1" spans="2:9">
@@ -13303,8 +13310,8 @@
       <c r="C436" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D436" s="23">
-        <v>29</v>
+      <c r="D436" s="17">
+        <v>44</v>
       </c>
       <c r="G436" s="16" t="s">
         <v>1001</v>
@@ -13312,8 +13319,8 @@
       <c r="H436" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="I436" s="23">
-        <v>29</v>
+      <c r="I436" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="437" ht="15" customHeight="1" spans="2:9">
@@ -13324,7 +13331,7 @@
         <v>124</v>
       </c>
       <c r="D437" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G437" s="16" t="s">
         <v>1003</v>
@@ -13333,7 +13340,7 @@
         <v>699</v>
       </c>
       <c r="I437" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="438" ht="15" customHeight="1" spans="2:9">
@@ -13343,8 +13350,8 @@
       <c r="C438" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D438" s="23">
-        <v>29</v>
+      <c r="D438" s="17">
+        <v>44</v>
       </c>
       <c r="G438" s="16" t="s">
         <v>1005</v>
@@ -13352,8 +13359,8 @@
       <c r="H438" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="I438" s="23">
-        <v>29</v>
+      <c r="I438" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="439" ht="15" customHeight="1" spans="2:9">
@@ -13364,7 +13371,7 @@
         <v>130</v>
       </c>
       <c r="D439" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G439" s="16" t="s">
         <v>1007</v>
@@ -13373,7 +13380,7 @@
         <v>705</v>
       </c>
       <c r="I439" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1" spans="2:9">
@@ -13383,8 +13390,8 @@
       <c r="C440" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D440" s="23">
-        <v>29</v>
+      <c r="D440" s="17">
+        <v>44</v>
       </c>
       <c r="G440" s="16" t="s">
         <v>1009</v>
@@ -13392,8 +13399,8 @@
       <c r="H440" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="I440" s="23">
-        <v>29</v>
+      <c r="I440" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="441" ht="15" customHeight="1" spans="2:9">
@@ -13404,7 +13411,7 @@
         <v>136</v>
       </c>
       <c r="D441" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G441" s="16" t="s">
         <v>1011</v>
@@ -13413,7 +13420,7 @@
         <v>711</v>
       </c>
       <c r="I441" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="442" ht="15" customHeight="1" spans="2:9">
@@ -13423,8 +13430,8 @@
       <c r="C442" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D442" s="23">
-        <v>29</v>
+      <c r="D442" s="17">
+        <v>44</v>
       </c>
       <c r="G442" s="16" t="s">
         <v>1013</v>
@@ -13432,8 +13439,8 @@
       <c r="H442" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="I442" s="23">
-        <v>29</v>
+      <c r="I442" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="443" ht="15" customHeight="1" spans="2:9">
@@ -13444,7 +13451,7 @@
         <v>142</v>
       </c>
       <c r="D443" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G443" s="16" t="s">
         <v>1015</v>
@@ -13453,7 +13460,7 @@
         <v>717</v>
       </c>
       <c r="I443" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="444" ht="15" customHeight="1" spans="2:9">
@@ -13463,8 +13470,8 @@
       <c r="C444" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D444" s="23">
-        <v>29</v>
+      <c r="D444" s="17">
+        <v>44</v>
       </c>
       <c r="G444" s="16" t="s">
         <v>1017</v>
@@ -13472,8 +13479,8 @@
       <c r="H444" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="I444" s="23">
-        <v>29</v>
+      <c r="I444" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1" spans="2:9">
@@ -13484,7 +13491,7 @@
         <v>148</v>
       </c>
       <c r="D445" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G445" s="16" t="s">
         <v>1019</v>
@@ -13493,7 +13500,7 @@
         <v>723</v>
       </c>
       <c r="I445" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="446" ht="15" customHeight="1" spans="2:9">
@@ -13503,8 +13510,8 @@
       <c r="C446" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D446" s="23">
-        <v>29</v>
+      <c r="D446" s="17">
+        <v>44</v>
       </c>
       <c r="G446" s="16" t="s">
         <v>1021</v>
@@ -13512,8 +13519,8 @@
       <c r="H446" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="I446" s="23">
-        <v>29</v>
+      <c r="I446" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="447" ht="15" customHeight="1" spans="2:9">
@@ -13524,7 +13531,7 @@
         <v>154</v>
       </c>
       <c r="D447" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G447" s="16" t="s">
         <v>1023</v>
@@ -13533,7 +13540,7 @@
         <v>729</v>
       </c>
       <c r="I447" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="448" ht="15" customHeight="1" spans="2:9">
@@ -13543,8 +13550,8 @@
       <c r="C448" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D448" s="23">
-        <v>29</v>
+      <c r="D448" s="17">
+        <v>44</v>
       </c>
       <c r="G448" s="16" t="s">
         <v>1025</v>
@@ -13552,8 +13559,8 @@
       <c r="H448" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="I448" s="23">
-        <v>29</v>
+      <c r="I448" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="449" ht="15" customHeight="1" spans="2:9">
@@ -13564,7 +13571,7 @@
         <v>160</v>
       </c>
       <c r="D449" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G449" s="16" t="s">
         <v>1027</v>
@@ -13573,7 +13580,7 @@
         <v>735</v>
       </c>
       <c r="I449" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1" spans="2:9">
@@ -13583,8 +13590,8 @@
       <c r="C450" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D450" s="23">
-        <v>29</v>
+      <c r="D450" s="17">
+        <v>44</v>
       </c>
       <c r="G450" s="16" t="s">
         <v>1029</v>
@@ -13592,8 +13599,8 @@
       <c r="H450" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="I450" s="23">
-        <v>29</v>
+      <c r="I450" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="451" ht="15" customHeight="1" spans="2:9">
@@ -13604,7 +13611,7 @@
         <v>166</v>
       </c>
       <c r="D451" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G451" s="16" t="s">
         <v>1031</v>
@@ -13613,7 +13620,7 @@
         <v>741</v>
       </c>
       <c r="I451" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="452" ht="15" customHeight="1" spans="2:9">
@@ -13623,8 +13630,8 @@
       <c r="C452" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D452" s="23">
-        <v>29</v>
+      <c r="D452" s="17">
+        <v>44</v>
       </c>
       <c r="G452" s="16" t="s">
         <v>1033</v>
@@ -13632,8 +13639,8 @@
       <c r="H452" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="I452" s="23">
-        <v>29</v>
+      <c r="I452" s="17">
+        <v>45</v>
       </c>
     </row>
     <row r="453" ht="15" customHeight="1" spans="2:9">
@@ -13644,7 +13651,7 @@
         <v>172</v>
       </c>
       <c r="D453" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G453" s="24" t="s">
         <v>1035</v>
@@ -13653,7 +13660,7 @@
         <v>747</v>
       </c>
       <c r="I453" s="17">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="454" ht="15" customHeight="1" spans="2:9">
@@ -13663,8 +13670,8 @@
       <c r="C454" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D454" s="14">
-        <v>30</v>
+      <c r="D454" s="17">
+        <v>9</v>
       </c>
       <c r="G454" s="12" t="s">
         <v>749</v>
@@ -13672,8 +13679,8 @@
       <c r="H454" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="I454" s="14">
-        <v>30</v>
+      <c r="I454" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1" spans="2:9">
@@ -13684,7 +13691,7 @@
         <v>180</v>
       </c>
       <c r="D455" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G455" s="16" t="s">
         <v>752</v>
@@ -13693,7 +13700,7 @@
         <v>753</v>
       </c>
       <c r="I455" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="456" ht="15" customHeight="1" spans="2:9">
@@ -13703,8 +13710,8 @@
       <c r="C456" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D456" s="14">
-        <v>30</v>
+      <c r="D456" s="17">
+        <v>9</v>
       </c>
       <c r="G456" s="16" t="s">
         <v>755</v>
@@ -13712,8 +13719,8 @@
       <c r="H456" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="I456" s="14">
-        <v>30</v>
+      <c r="I456" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="457" ht="15" customHeight="1" spans="2:9">
@@ -13724,7 +13731,7 @@
         <v>188</v>
       </c>
       <c r="D457" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G457" s="16" t="s">
         <v>758</v>
@@ -13733,7 +13740,7 @@
         <v>759</v>
       </c>
       <c r="I457" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="458" ht="15" customHeight="1" spans="2:9">
@@ -13743,8 +13750,8 @@
       <c r="C458" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D458" s="14">
-        <v>30</v>
+      <c r="D458" s="17">
+        <v>9</v>
       </c>
       <c r="G458" s="16" t="s">
         <v>761</v>
@@ -13752,8 +13759,8 @@
       <c r="H458" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="I458" s="14">
-        <v>30</v>
+      <c r="I458" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="459" ht="15" customHeight="1" spans="2:9">
@@ -13764,7 +13771,7 @@
         <v>196</v>
       </c>
       <c r="D459" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G459" s="16" t="s">
         <v>764</v>
@@ -13773,7 +13780,7 @@
         <v>765</v>
       </c>
       <c r="I459" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1" spans="2:9">
@@ -13783,8 +13790,8 @@
       <c r="C460" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D460" s="14">
-        <v>30</v>
+      <c r="D460" s="17">
+        <v>9</v>
       </c>
       <c r="G460" s="16" t="s">
         <v>767</v>
@@ -13792,8 +13799,8 @@
       <c r="H460" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="I460" s="14">
-        <v>30</v>
+      <c r="I460" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="461" ht="15" customHeight="1" spans="2:9">
@@ -13804,7 +13811,7 @@
         <v>204</v>
       </c>
       <c r="D461" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G461" s="16" t="s">
         <v>770</v>
@@ -13813,7 +13820,7 @@
         <v>771</v>
       </c>
       <c r="I461" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="462" ht="15" customHeight="1" spans="2:9">
@@ -13823,8 +13830,8 @@
       <c r="C462" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D462" s="14">
-        <v>30</v>
+      <c r="D462" s="17">
+        <v>9</v>
       </c>
       <c r="G462" s="16" t="s">
         <v>773</v>
@@ -13832,8 +13839,8 @@
       <c r="H462" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="I462" s="14">
-        <v>30</v>
+      <c r="I462" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="463" ht="15" customHeight="1" spans="2:9">
@@ -13844,7 +13851,7 @@
         <v>212</v>
       </c>
       <c r="D463" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G463" s="16" t="s">
         <v>776</v>
@@ -13853,7 +13860,7 @@
         <v>777</v>
       </c>
       <c r="I463" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="464" ht="15" customHeight="1" spans="2:9">
@@ -13863,8 +13870,8 @@
       <c r="C464" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D464" s="14">
-        <v>30</v>
+      <c r="D464" s="17">
+        <v>9</v>
       </c>
       <c r="G464" s="16" t="s">
         <v>779</v>
@@ -13872,8 +13879,8 @@
       <c r="H464" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="I464" s="14">
-        <v>30</v>
+      <c r="I464" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1" spans="2:9">
@@ -13884,7 +13891,7 @@
         <v>220</v>
       </c>
       <c r="D465" s="17">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G465" s="18" t="s">
         <v>782</v>
@@ -13893,7 +13900,7 @@
         <v>783</v>
       </c>
       <c r="I465" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="466" ht="15" customHeight="1" spans="2:9">
@@ -13903,8 +13910,8 @@
       <c r="C466" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D466" s="23">
-        <v>31</v>
+      <c r="D466" s="17">
+        <v>11</v>
       </c>
       <c r="G466" s="21" t="s">
         <v>785</v>
@@ -13912,8 +13919,8 @@
       <c r="H466" s="22" t="s">
         <v>786</v>
       </c>
-      <c r="I466" s="23">
-        <v>31</v>
+      <c r="I466" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="467" ht="15" customHeight="1" spans="2:9">
@@ -13924,7 +13931,7 @@
         <v>228</v>
       </c>
       <c r="D467" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G467" s="16" t="s">
         <v>788</v>
@@ -13933,7 +13940,7 @@
         <v>789</v>
       </c>
       <c r="I467" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="468" ht="15" customHeight="1" spans="2:9">
@@ -13943,8 +13950,8 @@
       <c r="C468" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D468" s="23">
-        <v>31</v>
+      <c r="D468" s="17">
+        <v>11</v>
       </c>
       <c r="G468" s="16" t="s">
         <v>791</v>
@@ -13952,8 +13959,8 @@
       <c r="H468" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="I468" s="23">
-        <v>31</v>
+      <c r="I468" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="469" ht="15" customHeight="1" spans="2:9">
@@ -13964,7 +13971,7 @@
         <v>236</v>
       </c>
       <c r="D469" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G469" s="16" t="s">
         <v>794</v>
@@ -13973,7 +13980,7 @@
         <v>795</v>
       </c>
       <c r="I469" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1" spans="2:9">
@@ -13983,8 +13990,8 @@
       <c r="C470" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D470" s="23">
-        <v>31</v>
+      <c r="D470" s="17">
+        <v>11</v>
       </c>
       <c r="G470" s="16" t="s">
         <v>797</v>
@@ -13992,8 +13999,8 @@
       <c r="H470" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="I470" s="23">
-        <v>31</v>
+      <c r="I470" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="471" ht="15" customHeight="1" spans="2:9">
@@ -14004,7 +14011,7 @@
         <v>244</v>
       </c>
       <c r="D471" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G471" s="16" t="s">
         <v>800</v>
@@ -14013,7 +14020,7 @@
         <v>801</v>
       </c>
       <c r="I471" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="472" ht="15" customHeight="1" spans="2:9">
@@ -14023,8 +14030,8 @@
       <c r="C472" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D472" s="23">
-        <v>31</v>
+      <c r="D472" s="17">
+        <v>11</v>
       </c>
       <c r="G472" s="16" t="s">
         <v>803</v>
@@ -14032,8 +14039,8 @@
       <c r="H472" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="I472" s="23">
-        <v>31</v>
+      <c r="I472" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="473" ht="15" customHeight="1" spans="2:9">
@@ -14044,7 +14051,7 @@
         <v>252</v>
       </c>
       <c r="D473" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G473" s="16" t="s">
         <v>806</v>
@@ -14053,7 +14060,7 @@
         <v>807</v>
       </c>
       <c r="I473" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="474" ht="15" customHeight="1" spans="2:9">
@@ -14063,8 +14070,8 @@
       <c r="C474" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D474" s="23">
-        <v>31</v>
+      <c r="D474" s="17">
+        <v>11</v>
       </c>
       <c r="G474" s="16" t="s">
         <v>809</v>
@@ -14072,8 +14079,8 @@
       <c r="H474" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="I474" s="23">
-        <v>31</v>
+      <c r="I474" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1" spans="2:9">
@@ -14084,7 +14091,7 @@
         <v>260</v>
       </c>
       <c r="D475" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G475" s="16" t="s">
         <v>812</v>
@@ -14093,7 +14100,7 @@
         <v>813</v>
       </c>
       <c r="I475" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="476" ht="15" customHeight="1" spans="2:9">
@@ -14103,8 +14110,8 @@
       <c r="C476" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D476" s="23">
-        <v>31</v>
+      <c r="D476" s="17">
+        <v>11</v>
       </c>
       <c r="G476" s="16" t="s">
         <v>815</v>
@@ -14112,8 +14119,8 @@
       <c r="H476" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="I476" s="23">
-        <v>31</v>
+      <c r="I476" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="477" ht="15" customHeight="1" spans="2:9">
@@ -14124,7 +14131,7 @@
         <v>268</v>
       </c>
       <c r="D477" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G477" s="16" t="s">
         <v>818</v>
@@ -14133,7 +14140,7 @@
         <v>819</v>
       </c>
       <c r="I477" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="478" ht="15" customHeight="1" spans="2:9">
@@ -14143,8 +14150,8 @@
       <c r="C478" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D478" s="23">
-        <v>31</v>
+      <c r="D478" s="17">
+        <v>11</v>
       </c>
       <c r="G478" s="16" t="s">
         <v>821</v>
@@ -14152,8 +14159,8 @@
       <c r="H478" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="I478" s="23">
-        <v>31</v>
+      <c r="I478" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="479" ht="15" customHeight="1" spans="2:9">
@@ -14164,7 +14171,7 @@
         <v>276</v>
       </c>
       <c r="D479" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G479" s="16" t="s">
         <v>824</v>
@@ -14173,7 +14180,7 @@
         <v>825</v>
       </c>
       <c r="I479" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1" spans="2:9">
@@ -14183,8 +14190,8 @@
       <c r="C480" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D480" s="23">
-        <v>31</v>
+      <c r="D480" s="17">
+        <v>11</v>
       </c>
       <c r="G480" s="16" t="s">
         <v>827</v>
@@ -14192,8 +14199,8 @@
       <c r="H480" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="I480" s="23">
-        <v>31</v>
+      <c r="I480" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="481" ht="15" customHeight="1" spans="2:9">
@@ -14204,7 +14211,7 @@
         <v>284</v>
       </c>
       <c r="D481" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G481" s="16" t="s">
         <v>830</v>
@@ -14213,7 +14220,7 @@
         <v>831</v>
       </c>
       <c r="I481" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="482" ht="15" customHeight="1" spans="2:9">
@@ -14223,8 +14230,8 @@
       <c r="C482" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D482" s="23">
-        <v>31</v>
+      <c r="D482" s="17">
+        <v>11</v>
       </c>
       <c r="G482" s="16" t="s">
         <v>833</v>
@@ -14232,8 +14239,8 @@
       <c r="H482" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="I482" s="23">
-        <v>31</v>
+      <c r="I482" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="483" ht="15" customHeight="1" spans="2:9">
@@ -14244,7 +14251,7 @@
         <v>292</v>
       </c>
       <c r="D483" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G483" s="16" t="s">
         <v>836</v>
@@ -14253,7 +14260,7 @@
         <v>837</v>
       </c>
       <c r="I483" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="484" ht="15" customHeight="1" spans="2:9">
@@ -14263,8 +14270,8 @@
       <c r="C484" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D484" s="23">
-        <v>31</v>
+      <c r="D484" s="17">
+        <v>11</v>
       </c>
       <c r="G484" s="16" t="s">
         <v>839</v>
@@ -14272,8 +14279,8 @@
       <c r="H484" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="I484" s="23">
-        <v>31</v>
+      <c r="I484" s="17">
+        <v>30</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1" spans="2:9">
@@ -14284,7 +14291,7 @@
         <v>300</v>
       </c>
       <c r="D485" s="17">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G485" s="24" t="s">
         <v>842</v>
@@ -14293,7 +14300,7 @@
         <v>843</v>
       </c>
       <c r="I485" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="486" ht="15" customHeight="1" spans="2:9">
@@ -14303,8 +14310,8 @@
       <c r="C486" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D486" s="14">
-        <v>32</v>
+      <c r="D486" s="17">
+        <v>13</v>
       </c>
       <c r="G486" s="12" t="s">
         <v>845</v>
@@ -14312,7 +14319,7 @@
       <c r="H486" s="13" t="s">
         <v>846</v>
       </c>
-      <c r="I486" s="14">
+      <c r="I486" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14324,7 +14331,7 @@
         <v>308</v>
       </c>
       <c r="D487" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G487" s="16" t="s">
         <v>847</v>
@@ -14343,8 +14350,8 @@
       <c r="C488" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D488" s="14">
-        <v>32</v>
+      <c r="D488" s="17">
+        <v>13</v>
       </c>
       <c r="G488" s="16" t="s">
         <v>849</v>
@@ -14352,7 +14359,7 @@
       <c r="H488" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="I488" s="14">
+      <c r="I488" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14364,7 +14371,7 @@
         <v>316</v>
       </c>
       <c r="D489" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G489" s="16" t="s">
         <v>851</v>
@@ -14383,8 +14390,8 @@
       <c r="C490" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D490" s="14">
-        <v>32</v>
+      <c r="D490" s="17">
+        <v>13</v>
       </c>
       <c r="G490" s="16" t="s">
         <v>853</v>
@@ -14392,7 +14399,7 @@
       <c r="H490" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="I490" s="14">
+      <c r="I490" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14404,7 +14411,7 @@
         <v>324</v>
       </c>
       <c r="D491" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G491" s="16" t="s">
         <v>855</v>
@@ -14423,8 +14430,8 @@
       <c r="C492" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D492" s="14">
-        <v>32</v>
+      <c r="D492" s="17">
+        <v>13</v>
       </c>
       <c r="G492" s="16" t="s">
         <v>857</v>
@@ -14432,7 +14439,7 @@
       <c r="H492" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="I492" s="14">
+      <c r="I492" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14444,7 +14451,7 @@
         <v>332</v>
       </c>
       <c r="D493" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G493" s="16" t="s">
         <v>859</v>
@@ -14463,8 +14470,8 @@
       <c r="C494" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D494" s="14">
-        <v>32</v>
+      <c r="D494" s="17">
+        <v>13</v>
       </c>
       <c r="G494" s="16" t="s">
         <v>861</v>
@@ -14472,7 +14479,7 @@
       <c r="H494" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="I494" s="14">
+      <c r="I494" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14484,7 +14491,7 @@
         <v>340</v>
       </c>
       <c r="D495" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G495" s="16" t="s">
         <v>863</v>
@@ -14503,8 +14510,8 @@
       <c r="C496" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D496" s="14">
-        <v>32</v>
+      <c r="D496" s="17">
+        <v>13</v>
       </c>
       <c r="G496" s="16" t="s">
         <v>865</v>
@@ -14512,7 +14519,7 @@
       <c r="H496" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="I496" s="14">
+      <c r="I496" s="17">
         <v>32</v>
       </c>
     </row>
@@ -14524,7 +14531,7 @@
         <v>348</v>
       </c>
       <c r="D497" s="17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G497" s="18" t="s">
         <v>867</v>
@@ -14543,8 +14550,8 @@
       <c r="C498" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="D498" s="23">
-        <v>33</v>
+      <c r="D498" s="17">
+        <v>15</v>
       </c>
       <c r="G498" s="21" t="s">
         <v>869</v>
@@ -14552,7 +14559,7 @@
       <c r="H498" s="22" t="s">
         <v>870</v>
       </c>
-      <c r="I498" s="23">
+      <c r="I498" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14564,7 +14571,7 @@
         <v>356</v>
       </c>
       <c r="D499" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G499" s="16" t="s">
         <v>871</v>
@@ -14583,8 +14590,8 @@
       <c r="C500" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D500" s="23">
-        <v>33</v>
+      <c r="D500" s="17">
+        <v>15</v>
       </c>
       <c r="G500" s="16" t="s">
         <v>873</v>
@@ -14592,7 +14599,7 @@
       <c r="H500" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="I500" s="23">
+      <c r="I500" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14604,7 +14611,7 @@
         <v>364</v>
       </c>
       <c r="D501" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G501" s="16" t="s">
         <v>875</v>
@@ -14623,8 +14630,8 @@
       <c r="C502" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D502" s="23">
-        <v>33</v>
+      <c r="D502" s="17">
+        <v>15</v>
       </c>
       <c r="G502" s="16" t="s">
         <v>877</v>
@@ -14632,7 +14639,7 @@
       <c r="H502" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="I502" s="23">
+      <c r="I502" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14644,7 +14651,7 @@
         <v>372</v>
       </c>
       <c r="D503" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G503" s="16" t="s">
         <v>879</v>
@@ -14663,8 +14670,8 @@
       <c r="C504" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D504" s="23">
-        <v>33</v>
+      <c r="D504" s="17">
+        <v>15</v>
       </c>
       <c r="G504" s="16" t="s">
         <v>881</v>
@@ -14672,7 +14679,7 @@
       <c r="H504" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="I504" s="23">
+      <c r="I504" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14684,7 +14691,7 @@
         <v>380</v>
       </c>
       <c r="D505" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G505" s="16" t="s">
         <v>883</v>
@@ -14703,8 +14710,8 @@
       <c r="C506" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D506" s="23">
-        <v>33</v>
+      <c r="D506" s="17">
+        <v>15</v>
       </c>
       <c r="G506" s="16" t="s">
         <v>885</v>
@@ -14712,7 +14719,7 @@
       <c r="H506" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="I506" s="23">
+      <c r="I506" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14724,7 +14731,7 @@
         <v>388</v>
       </c>
       <c r="D507" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G507" s="16" t="s">
         <v>887</v>
@@ -14743,8 +14750,8 @@
       <c r="C508" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D508" s="23">
-        <v>33</v>
+      <c r="D508" s="17">
+        <v>15</v>
       </c>
       <c r="G508" s="16" t="s">
         <v>889</v>
@@ -14752,7 +14759,7 @@
       <c r="H508" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="I508" s="23">
+      <c r="I508" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14764,7 +14771,7 @@
         <v>396</v>
       </c>
       <c r="D509" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G509" s="16" t="s">
         <v>891</v>
@@ -14783,8 +14790,8 @@
       <c r="C510" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D510" s="23">
-        <v>33</v>
+      <c r="D510" s="17">
+        <v>15</v>
       </c>
       <c r="G510" s="16" t="s">
         <v>893</v>
@@ -14792,7 +14799,7 @@
       <c r="H510" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="I510" s="23">
+      <c r="I510" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14804,7 +14811,7 @@
         <v>404</v>
       </c>
       <c r="D511" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G511" s="16" t="s">
         <v>895</v>
@@ -14823,8 +14830,8 @@
       <c r="C512" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D512" s="23">
-        <v>33</v>
+      <c r="D512" s="17">
+        <v>15</v>
       </c>
       <c r="G512" s="16" t="s">
         <v>897</v>
@@ -14832,7 +14839,7 @@
       <c r="H512" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="I512" s="23">
+      <c r="I512" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14844,7 +14851,7 @@
         <v>412</v>
       </c>
       <c r="D513" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G513" s="16" t="s">
         <v>899</v>
@@ -14863,8 +14870,8 @@
       <c r="C514" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D514" s="23">
-        <v>33</v>
+      <c r="D514" s="17">
+        <v>15</v>
       </c>
       <c r="G514" s="16" t="s">
         <v>901</v>
@@ -14872,7 +14879,7 @@
       <c r="H514" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="I514" s="23">
+      <c r="I514" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14884,7 +14891,7 @@
         <v>420</v>
       </c>
       <c r="D515" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G515" s="16" t="s">
         <v>903</v>
@@ -14903,8 +14910,8 @@
       <c r="C516" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D516" s="23">
-        <v>33</v>
+      <c r="D516" s="17">
+        <v>15</v>
       </c>
       <c r="G516" s="16" t="s">
         <v>905</v>
@@ -14912,7 +14919,7 @@
       <c r="H516" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="I516" s="23">
+      <c r="I516" s="17">
         <v>33</v>
       </c>
     </row>
@@ -14924,7 +14931,7 @@
         <v>428</v>
       </c>
       <c r="D517" s="17">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G517" s="24" t="s">
         <v>907</v>
